--- a/docs/helsinki-aug-2026/Helsinki-16-20-Aug-2026.xlsx
+++ b/docs/helsinki-aug-2026/Helsinki-16-20-Aug-2026.xlsx
@@ -21,15 +21,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_Itinerary'!$A$1:$J$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_Book_tonight'!$A$1:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Restaurants'!$A$1:$Q$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_Arrival_brunch'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Activities'!$A$1:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_Book_tonight'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Restaurants'!$A$1:$Q$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_Arrival_brunch'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Activities'!$A$1:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_Tours_bookable'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_Open_matrix'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_Open_matrix'!$A$1:$G$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_Rain_and_skip'!$A$1:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_Viz_data'!$A$1:$C$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_Sources'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_Viz_data'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_Sources'!$A$1:$E$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -324,12 +324,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'09_Viz_data'!$A$2:$A$17</f>
+              <f>'09_Viz_data'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'09_Viz_data'!$B$2:$B$17</f>
+              <f>'09_Viz_data'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -1025,7 +1025,7 @@
           <t>SUN 16  Ekberg/Fazer brunch → Amos Rex (closed Tue; Sun 11–17) → Oodi (Sun 10–20) → Georgian Kitchen.
 MON 17  Suomenlinna (HSL ferry, Blue Route). Evening: Katana ramen (likely closed Sun) or Kallio.
 TUE 18  ADM Design Museum (Rex closed). Lunch: Levain Ullanlinna next door. Dinner: Nolla.
-WED 19  Löyly sauna + Baltic. Dinner: Grön if the table exists, else Latitude 25 / Shii.
+WED 19  Löyly sauna + Baltic. Dinner: Skörd 86e (rational) or Grön 188e if a table exists.
 THU 20  Buffer. Ateneum is FREE 10:00–20:00 this day — only if departure mode allows. Out by 15:00.</t>
         </is>
       </c>
@@ -1199,11 +1199,11 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Katana Ramen</t>
+          <t>Skörd</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Sea Horse</t>
+          <t>Katana Ramen</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -1229,7 +1229,7 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Gaijin</t>
+          <t>Sea Horse</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -1244,22 +1244,22 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Oodi</t>
+          <t>Gaijin</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Meal</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Latitude / Shii</t>
+          <t>Oodi</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -1267,50 +1267,65 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Meal</t>
+          <t>Place</t>
         </is>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Ateneum free Thu</t>
+          <t>Latitude / Shii</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Meal</t>
         </is>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Cathedral day</t>
+          <t>Ateneum free Thu</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Place</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
+          <t>Cathedral day</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
           <t>Momotoko</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Skip</t>
         </is>
@@ -1385,7 +1400,7 @@
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1395,7 +1410,7 @@
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1409,8 +1424,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C17"/>
-  <conditionalFormatting sqref="B2:B17">
+  <autoFilter ref="A1:C18"/>
+  <conditionalFormatting sqref="B2:B18">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1434,7 +1449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1749,12 +1764,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Latitude 25 hours</t>
+          <t>Latitude 25 hours + 119e booking</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>https://www.latitude25.fi/</t>
+          <t>https://www.latitude25.fi/booking/</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1771,17 +1786,17 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>S-shii</t>
+          <t>S-skord</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Shii concept + phone</t>
+          <t>Skörd menu 86e / 72e</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>https://shii.fi/</t>
+          <t>https://xn--skrd-6qa.fi/en/food/</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1791,24 +1806,24 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>High concept; hours missing</t>
+          <t>High — official</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>S-seahorse</t>
+          <t>S-kuurna</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Sea Horse summer hours</t>
+          <t>Kuurna hours + 46e/54e</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>https://www.seahorse.fi/en/restaurant-sea-horse/</t>
+          <t>https://www.kuurna.fi/in-english</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1825,17 +1840,17 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>S-kosmos</t>
+          <t>S-muru</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Kosmos hours + menu</t>
+          <t>Muru menu of the day 59e</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>https://kosmos.fi/en/our-food/</t>
+          <t>https://murudining.fi/en/</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1845,24 +1860,24 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>High — official</t>
+          <t>High price; closed days VERIFY</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>S-elite</t>
+          <t>S-aalto</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Elite hours</t>
+          <t>Aalto House guided tours</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>https://elite.fi/en/front-page/</t>
+          <t>https://www.alvaraalto.fi/en/location/the-aalto-house/</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1879,17 +1894,17 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>S-bui</t>
+          <t>S-ksauna</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Bui Ramen hours + prices</t>
+          <t>Kulttuurisauna hours + €17</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>https://buiramen.fi/</t>
+          <t>https://www.kulttuurisauna.fi/</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1906,17 +1921,17 @@
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>S-levain</t>
+          <t>S-shii</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Levain branch hours</t>
+          <t>Shii concept + phone</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>https://www.levain.fi/reservation</t>
+          <t>https://shii.fi/</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1926,24 +1941,24 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>High — official</t>
+          <t>High concept; hours missing</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>S-loyly</t>
+          <t>S-seahorse</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Löyly sauna price + rules</t>
+          <t>Sea Horse summer hours</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>https://www.loylyhelsinki.fi/en/public-sauna</t>
+          <t>https://www.seahorse.fi/en/restaurant-sea-horse/</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1960,17 +1975,17 @@
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>S-loyly-h</t>
+          <t>S-kosmos</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Löyly weekly hours</t>
+          <t>Kosmos hours + menu</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>https://www.loylyhelsinki.fi/en/info</t>
+          <t>https://kosmos.fi/en/our-food/</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1987,17 +2002,17 @@
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>S-rex</t>
+          <t>S-elite</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Amos Rex hours</t>
+          <t>Elite hours</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>https://amosrex.fi/en/visit-us/</t>
+          <t>https://elite.fi/en/front-page/</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2014,17 +2029,17 @@
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>S-rex-t</t>
+          <t>S-bui</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Amos Rex tickets</t>
+          <t>Bui Ramen hours + prices</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>https://amosrex.fi/en/tickets/</t>
+          <t>https://buiramen.fi/</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -2041,17 +2056,17 @@
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>S-adm</t>
+          <t>S-levain</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>ADM hours + construction</t>
+          <t>Levain branch hours</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>https://admuseo.fi/en/visit-us/</t>
+          <t>https://www.levain.fi/reservation</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2068,17 +2083,17 @@
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>S-oodi</t>
+          <t>S-loyly</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Oodi hours 2026</t>
+          <t>Löyly sauna price + rules</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>https://oodihelsinki.fi/en/arrival/</t>
+          <t>https://www.loylyhelsinki.fi/en/public-sauna</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -2095,17 +2110,17 @@
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>S-hsl</t>
+          <t>S-loyly-h</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>HSL Suomenlinna ferry</t>
+          <t>Löyly weekly hours</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>https://www.hsl.fi/en/travelling/visitors/suomenlinna</t>
+          <t>https://www.loylyhelsinki.fi/en/info</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2115,24 +2130,24 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>High — official; fare can move</t>
+          <t>High — official</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>S-sl-arr</t>
+          <t>S-rex</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Suomenlinna arriving</t>
+          <t>Amos Rex hours</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>https://suomenlinna.fi/en/explore/arriving/</t>
+          <t>https://amosrex.fi/en/visit-us/</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -2149,17 +2164,17 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>S-sl-tour</t>
+          <t>S-rex-t</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>English guided tour 2026</t>
+          <t>Amos Rex tickets</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>https://suomenlinna.johku.com/en_US/liput/guided-walking-tour-in-english</t>
+          <t>https://amosrex.fi/en/tickets/</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2169,24 +2184,24 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>High schedule; inventory unknown</t>
+          <t>High — official</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>S-ateneum</t>
+          <t>S-adm</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Ateneum hours + free 20 Aug</t>
+          <t>ADM hours + construction</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>https://ateneum.fi/en/opening-hours-and-tickets/</t>
+          <t>https://admuseo.fi/en/visit-us/</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2203,17 +2218,17 @@
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>S-allas</t>
+          <t>S-oodi</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Allas hours</t>
+          <t>Oodi hours 2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>https://allasseapool.fi/en/</t>
+          <t>https://oodihelsinki.fi/en/arrival/</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -2230,59 +2245,410 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>S-momo</t>
+          <t>S-hsl</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Momotoko bankruptcy</t>
+          <t>HSL Suomenlinna ferry</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>https://www.hs.fi/helsinki/art-2000011230551.html</t>
+          <t>https://www.hsl.fi/en/travelling/visitors/suomenlinna</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>High — local press, closure status</t>
+          <t>High — official; fare can move</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>S-sl-arr</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Suomenlinna arriving</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>https://suomenlinna.fi/en/explore/arriving/</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>S-sl-tour</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>English guided tour 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>https://suomenlinna.johku.com/en_US/liput/guided-walking-tour-in-english</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>High schedule; inventory unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>S-ateneum</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Ateneum hours + free 20 Aug</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>https://ateneum.fi/en/opening-hours-and-tickets/</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>S-allas</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Allas hours</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>https://allasseapool.fi/en/</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>S-momo</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Momotoko bankruptcy</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hs.fi/helsinki/art-2000011230551.html</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>High — local press, closure status</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
           <t>S-katana</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Katana hours (Falstaff)</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>https://www.falstaff.com/at/streetfood/katana-ramen-restaurant</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>Medium — secondary, no official hours page</t>
         </is>
       </c>
     </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>S-sansar</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Sansar hours (ex-Satkar)</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sansar.fi/</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>S-mountain</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Restaurant Mountain hours</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>https://ravintolamountain.com/en/home/</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>S-basbas</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>BasBas hours</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>https://basbas.fi/bistro/en/</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>S-cella</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Cella hours through 17 Aug</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ravintolacella.fi/</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>High Sun–Mon; Tue–Thu unverified</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>S-carelia</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Carelia hours + 2026 summer break</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>https://ravintolacarelia.fi/en/home-2/</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>S-harju8</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Harju 8 listing</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>https://www.myhelsinki.fi/places/harju-8/</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Medium — MyHelsinki; kitchen close missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>S-lohtu</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Lohtu hall lunch hours</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ravintolalohtu.fi/en/</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>S-nbhd</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Neighbourhood eateries research (40 venues)</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>docs/helsinki-aug-2026/research/neighbourhood-eateries.md</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Compiled from official/MyHelsinki/HS — VERIFY live</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E31"/>
+  <autoFilter ref="A1:E44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -2314,6 +2680,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2936,7 +3314,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>GRÖN, Albertinkatu 36 — YOUR ONLY NIGHT (closed Sun–Tue). Official summer 2026 menu 188e (omnivore or vegan preorder). Else Latitude 25 omakase (Albertinkatu 19, Wed–Thu 17–21:30) or Shii (Fabianinkatu 17, 16 seats, not vegetarian).</t>
+          <t>SKÖRD (Fredrikinkatu 37) is the rational splurge: official seven-course 86e, Mon–Thu four-course 72e, Finnish ingredients only. GRÖN (Albertinkatu 36) is 188e and Wednesday-only. Else Latitude 25 omakase 119e official (not vegetarian) or Shii.</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2946,12 +3324,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Grön set 188e / Latitude omakase / Shii 11-course</t>
+          <t>Skörd 86e / Grön 188e / Latitude 119e</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>BOOK DinnerBooking Grön; latitude25.fi; shii.fi — take whichever confirms</t>
+          <t>BOOK Skörd TableOnline AND/OR Grön DinnerBooking — take one</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -2961,7 +3339,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>Olo/Palace/Finnjävel blow more. Finnjävel Tue–Sat; skip unless you decide to.</t>
+          <t>Olo Selected 109e / Palace 250e — only if you decide to. Skörd cannot do vegan/dairy-free.</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3296,7 +3674,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Latitude 25 / Shii / unused Nolla</t>
+          <t>Skörd 86e / Latitude 25 / unused Nolla</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -3308,341 +3686,467 @@
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3b</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Löyly 2h public sauna</t>
+          <t>Skörd</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Wed 19 13:00+</t>
+          <t>Wed 19 (also Mon–Tue; closed Sun)</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Official calendar</t>
+          <t>TableOnline</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>https://varaus.asio.fi/onlinekalenteri/loyly/guest.php?ss_lang=eng</t>
+          <t>https://www.tableonline.fi/en/helsinki/skord/1001/book</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>+358 50 4768741 sauna</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Allas Sea Pool</t>
+          <t>Kuurna / Nolla / Muru</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>YES — architecture + Baltic</t>
+          <t>YES if 188e is too much — official menu 86e; Mon–Thu 4-course 72e</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3c</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Gaijin</t>
+          <t>Kuurna</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Sun from 15:00 or later</t>
+          <t>Mon 17 dinner (open Mon; Nolla is not)</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Official reservation</t>
+          <t>Official site / phone</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>https://www.gaijin.fi/reservation</t>
+          <t>https://www.kuurna.fi/in-english</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>010 322 9386 / same-day 010 322 9381</t>
+          <t>+358 44 755 4555</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Nolla</t>
+          <t>Sea Horse / Kosmos</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Strong alt, not Georgian</t>
+          <t>Strong Mon neighbourhood bistro — 2/3 courses from 46e/54e official</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Latitude 25</t>
+          <t>Löyly 2h public sauna</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Wed 19 (closed Sun–Tue)</t>
+          <t>Wed 19 13:00+</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Call / site</t>
+          <t>Official calendar</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>https://www.latitude25.fi/</t>
+          <t>https://varaus.asio.fi/onlinekalenteri/loyly/guest.php?ss_lang=eng</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>+358 9 6128 6000</t>
+          <t>+358 50 4768741 sauna</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Shii https://shii.fi/ 050 329 0360</t>
+          <t>Kulttuurisauna (quieter, €17/90 min, Wed–Sun 16–20) or Allas</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Only if Grön fails and you want omakase</t>
+          <t>YES — architecture + Baltic</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Sea Horse</t>
+          <t>Gaijin</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Any dinner from 15:00</t>
+          <t>Sun from 15:00 or later</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Online / phone</t>
+          <t>Official reservation</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>https://www.seahorse.fi/en/restaurant-sea-horse/</t>
+          <t>https://www.gaijin.fi/reservation</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>+358 9 628 169</t>
+          <t>010 322 9386 / same-day 010 322 9381</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Walk-in off-peak possible</t>
+          <t>Nolla</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Finnish classic backup</t>
+          <t>Strong alt, not Georgian</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Amos Rex ticket</t>
+          <t>Latitude 25</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Sun 16 before 17:00</t>
+          <t>Wed 19 (closed Sun–Tue)</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Official tickets</t>
+          <t>Call / site</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>https://amosrex.fi/en/tickets/</t>
+          <t>https://www.latitude25.fi/</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>09 6844 460</t>
+          <t>+358 9 6128 6000</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Door; 18–29 / students €5 official</t>
+          <t>Shii https://shii.fi/ 050 329 0360</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>YES today — closed Tue</t>
+          <t>Only if Grön fails and you want omakase</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>HSL ticket / app</t>
+          <t>Sea Horse</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>All week inc Suomenlinna ferry</t>
+          <t>Any dinner from 15:00</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>HSL app or pier machine BEFORE boarding</t>
+          <t>Online / phone</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>https://www.hsl.fi/en/travelling/visitors/suomenlinna</t>
+          <t>https://www.seahorse.fi/en/restaurant-sea-horse/</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+358 9 628 169</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Contactless at readers</t>
+          <t>Walk-in off-peak possible</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Finnish classic backup</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Amos Rex ticket</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Sun 16 before 17:00</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Official tickets</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>https://amosrex.fi/en/tickets/</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>09 6844 460</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Door; 18–29 / students €5 official</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>YES today — closed Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>HSL ticket / app</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>All week inc Suomenlinna ferry</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>HSL app or pier machine BEFORE boarding</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hsl.fi/en/travelling/visitors/suomenlinna</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Contactless at readers</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Optional: Suomenlinna English tour</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Mon 17 10:30 / 12:30 / 14:30</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Ehrensvärd Society shop</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>https://suomenlinna.johku.com/en_US/liput/guided-walking-tour-in-english</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>+358 9 68999 850</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Self-guided Blue Route is enough</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>10b</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Optional: Aalto House</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Tue 18 11:00–16:00 hourly (Jul–Aug)</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Guided only; max 15; shop.alvaraalto.fi</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>https://shop.alvaraalto.fi/en_US/guided-tours/guided-tour-of-the-house</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>hello@alvaraalto.fi</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Skip and go straight to ADM</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Optional — Munkkiniemi; do not stack with a second museum if tired</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Do NOT book</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Cathedral tours, SkyWheel, food tours, Temppeliaukio as a day, ADM walk Thu 15:00</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>Skip</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -3655,6 +4159,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3667,7 +4174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4627,14 +5134,14 @@
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Latitude 25</t>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Skörd</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Omakase</t>
+          <t>Hyperlocal Finnish</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -4644,7 +5151,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Albertinkatu 19</t>
+          <t>Fredrikinkatu 37</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -4654,92 +5161,92 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>86e seven-course official; Mon–Thu 72e four-course</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Book TableOnline</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>CLOSED*</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>Dinner 17–00*</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>Dinner*</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>17:00–21:30</t>
+          <t>Dinner*</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>Leave 15:00</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>Billed as Finland's premier omakase. Only Wednesday for you.</t>
+          <t>Only Finnish ingredients (no pepper/avocado). The rational splurge under 100e. Not vegan/dairy-free.</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>Omakase counter</t>
+          <t>Seven-course 86e</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>https://www.latitude25.fi/</t>
+          <t>https://xn--skrd-6qa.fi/en/food/</t>
         </is>
       </c>
       <c r="P12" s="8" t="inlineStr">
         <is>
-          <t>Official hours</t>
+          <t>Official menu; hours Time Out Mon–Sat 17–00</t>
         </is>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Shii</t>
+          <t>Kuurna</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Omakase / otsumami</t>
+          <t>Nordic bistro</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Kaartinkaupunki</t>
+          <t>Kruununhaka</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Fabianinkatu 17</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>icon</t>
+          <t>Meritullinkatu 6</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>hot</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>2 courses from 46e; 3 from 54e official</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -4749,332 +5256,332 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>17–23 kitchen 21:00</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>17–23</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>17–23</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>Leave 15:00</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>16 seats; 11-course; cannot be made vegetarian</t>
+          <t>Open Monday when Nolla is shut. Menu 12.8–1.9.2026 on official page.</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>Counter</t>
+          <t>3 courses; tartare +4e</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>https://shii.fi/</t>
+          <t>https://www.kuurna.fi/in-english</t>
         </is>
       </c>
       <c r="P13" s="8" t="inlineStr">
         <is>
-          <t>Official concept; hours missing — VERIFY</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Domo</t>
+          <t>Muru</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Sushi à la carte</t>
+          <t>Bistro / wine</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Kamppi</t>
+          <t>Punavuori</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Kalevankatu 21</t>
+          <t>Fredrikinkatu 41</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>neighbourhood</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in / call</t>
+          <t>Menu of the Day 59e official</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Book</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CLOSED*</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CLOSED*</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>Dinner*</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>Dinner*</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>Long-running; more fish less rice; not buffet</t>
+          <t>Helsinki bistro classic. Closed days VERIFY (often Sun–Mon).</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>Nigiri</t>
-        </is>
-      </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY official site</t>
+          <t>Four-course 59e</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>https://murudining.fi/en/</t>
         </is>
       </c>
       <c r="P14" s="8" t="inlineStr">
         <is>
-          <t>Hours not captured — VERIFY</t>
+          <t>Official menu price; closed days VERIFY</t>
         </is>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Katana Ramen</t>
+          <t>Latitude 25</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Ramen</t>
+          <t>Omakase</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Punavuori / Telakka</t>
+          <t>Punavuori</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Telakkakatu 12</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>hot</t>
+          <t>Albertinkatu 19</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in</t>
+          <t>119e without drinks official</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Book mandatory</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>CLOSED?*</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>11–21*</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>11–21*</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>11–21*</t>
+          <t>17:00–21:30</t>
         </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>11–21*</t>
+          <t>Leave 15:00</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>Dedicated ramen after Momotoko died. HS reviewed Jul 2026.</t>
+          <t>14-seat counter. 119e card guarantee. Cannot do vegetarian/vegan/no-raw-fish.</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>Tonkotsu</t>
-        </is>
-      </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>katanaramenclub@gmail.com</t>
+          <t>Omakase</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>https://www.latitude25.fi/booking/</t>
         </is>
       </c>
       <c r="P15" s="8" t="inlineStr">
         <is>
-          <t>Falstaff hours (secondary)</t>
+          <t>Official hours + 2026 price</t>
         </is>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Bui Ramen</t>
+          <t>Shii</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Ramen / mazemen</t>
+          <t>Omakase / otsumami</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Kalasatama</t>
+          <t>Kaartinkaupunki</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Aallonhalkoja 1 L T 2</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>neighbourhood</t>
+          <t>Fabianinkatu 17</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Bui Paitan 17.90€ official</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in / book</t>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Book</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>12–20</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>Leave 15:00</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>Handmade noodles; not central — only if east</t>
+          <t>16 seats; 11-course; cannot be made vegetarian</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>Bui Paitan</t>
+          <t>Counter</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>https://buiramen.fi/</t>
+          <t>https://shii.fi/</t>
         </is>
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official concept; hours missing — VERIFY</t>
         </is>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Ramen Ichiraku</t>
+          <t>Domo</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Ramen</t>
+          <t>Sushi à la carte</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Kamppi mall 5F</t>
+          <t>Kamppi</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Urho Kekkosen katu 1</t>
+          <t>Kalevankatu 21</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>cheap-everyday</t>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -5084,82 +5591,82 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Walk-in</t>
+          <t>Walk-in / call</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>12–19</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>11–21 morning</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>Emergency bowl. Mall. Time Out: reliable, not soulful.</t>
+          <t>Long-running; more fish less rice; not buffet</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>Tonkotsu / tan tan</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="inlineStr">
-        <is>
-          <t>https://www.kamppihelsinki.fi/en/shops-and-services/other-stores/ramen-ichiraku/-/110</t>
+          <t>Nigiri</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY official site</t>
         </is>
       </c>
       <c r="P17" s="8" t="inlineStr">
         <is>
-          <t>Official Kamppi listing</t>
+          <t>Hours not captured — VERIFY</t>
         </is>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Sushi Wagocoro</t>
+          <t>Katana Ramen</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Sushi neighbourhood</t>
+          <t>Ramen</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Taka-Töölö</t>
+          <t>Punavuori / Telakka</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Runeberginkatu 63 A 21</t>
+          <t>Telakkakatu 12</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>neighbourhood</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -5167,79 +5674,79 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Book/call — tiny</t>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CLOSED?*</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21*</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21*</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21*</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21*</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>Japanese-owned small room. Confirm before crossing town.</t>
+          <t>Dedicated ramen after Momotoko died. HS reviewed Jul 2026.</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Nigiri</t>
-        </is>
-      </c>
-      <c r="O18" s="11" t="inlineStr">
-        <is>
-          <t>https://www.myhelsinki.fi/places/sushi-wagocoro/</t>
+          <t>Tonkotsu</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>katanaramenclub@gmail.com</t>
         </is>
       </c>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t>MyHelsinki — hours VERIFY</t>
+          <t>Falstaff hours (secondary)</t>
         </is>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Kabuki</t>
+          <t>Bui Ramen</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Traditional Japanese</t>
+          <t>Ramen / mazemen</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Kamppi</t>
+          <t>Kalasatama</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Lapinlahdenkatu 12</t>
+          <t>Aallonhalkoja 1 L T 2</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -5249,82 +5756,82 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Book — small room</t>
+          <t>Bui Paitan 17.90€ official</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in / book</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>12–20</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>Old-school Japanese / tatami, not Nordic omakase theatre</t>
+          <t>Handmade noodles; not central — only if east</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>Sushi / set</t>
+          <t>Bui Paitan</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>https://www.myhelsinki.fi/places/kabuki/</t>
+          <t>https://buiramen.fi/</t>
         </is>
       </c>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>MyHelsinki — hours VERIFY</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Sansar (ex-Satkar)</t>
+          <t>Ramen Ichiraku</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Nepalese</t>
+          <t>Ramen</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Kamppi</t>
+          <t>Kamppi mall 5F</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Fredrikinkatu 46</t>
+          <t>Urho Kekkosen katu 1</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -5339,67 +5846,67 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Walk-in lunch</t>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>12–21</t>
+          <t>12–19</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>10:30–21; lunch to 16</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>lunch if time</t>
+          <t>11–21 morning</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>Kamppi since 1998. Ordinary diaspora lunch. Search Sansar, not Satkar.</t>
+          <t>Emergency bowl. Mall. Time Out: reliable, not soulful.</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Tandoor / curry lunch</t>
+          <t>Tonkotsu / tan tan</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>https://www.sansar.fi/</t>
+          <t>https://www.kamppihelsinki.fi/en/shops-and-services/other-stores/ramen-ichiraku/-/110</t>
         </is>
       </c>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official Kamppi listing</t>
         </is>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Restaurant Mountain</t>
+          <t>Sushi Wagocoro</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Nepalese</t>
+          <t>Sushi neighbourhood</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -5409,12 +5916,12 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Nordenskiöldinkatu 8</t>
+          <t>Runeberginkatu 63 A 21</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>cheap-everyday</t>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -5422,84 +5929,84 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in lunch</t>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Book/call — tiny</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>12:30–22</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>10:30–22:30; lunch to 15</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>lunch if time</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>Family-owned since 2000. The kebabpizza analogue.</t>
+          <t>Japanese-owned small room. Confirm before crossing town.</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>Dal / tandoor</t>
+          <t>Nigiri</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>https://ravintolamountain.com/en/home/</t>
+          <t>https://www.myhelsinki.fi/places/sushi-wagocoro/</t>
         </is>
       </c>
       <c r="P21" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>MyHelsinki — hours VERIFY</t>
         </is>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>BasBas (Baskeri &amp; Basso)</t>
+          <t>Kabuki</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Bistro / natural wine</t>
+          <t>Traditional Japanese</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Punavuori</t>
+          <t>Kamppi</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Tehtaankatu 27–29 courtyard</t>
+          <t>Lapinlahdenkatu 12</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -5509,82 +6016,82 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Book — small room</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>from 16:00</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>from 16:00</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>too late</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>Ingredient-led small plates. Closed Sun–Mon so Tue/Wed.</t>
+          <t>Old-school Japanese / tatami, not Nordic omakase theatre</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Share plates + wine</t>
+          <t>Sushi / set</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>https://basbas.fi/bistro/en/</t>
+          <t>https://www.myhelsinki.fi/places/kabuki/</t>
         </is>
       </c>
       <c r="P22" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>MyHelsinki — hours VERIFY</t>
         </is>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Nolita</t>
+          <t>Sansar (ex-Satkar)</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Seasonal bistro / wine</t>
+          <t>Nepalese</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Punavuori</t>
+          <t>Kamppi</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Kankurinkatu 6</t>
+          <t>Fredrikinkatu 46</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>cheap-everyday</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -5592,49 +6099,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>Book dinner</t>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in lunch</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>12–21</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>10:30–21; lunch to 16</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>17–22</t>
+          <t>same</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>17–22</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>too late</t>
+          <t>lunch if time</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>Closed Sun–Mon. In-house sourdough with dinner.</t>
+          <t>Kamppi since 1998. Ordinary diaspora lunch. Search Sansar, not Satkar.</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>Shareable bistro</t>
+          <t>Tandoor / curry lunch</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>https://nolita.fi/en/</t>
+          <t>https://www.sansar.fi/</t>
         </is>
       </c>
       <c r="P23" s="8" t="inlineStr">
@@ -5643,33 +6150,33 @@
         </is>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>The Alley</t>
+          <t>Restaurant Mountain</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Small plates / wine</t>
+          <t>Nepalese</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Kallio</t>
+          <t>Taka-Töölö</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Fleminginkatu 8</t>
+          <t>Nordenskiöldinkatu 8</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>cheap-everyday</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -5677,49 +6184,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>Book / some walk-in</t>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in lunch</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>12:30–22</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>10:30–22:30; lunch to 15</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>17–23 kitchen 21:30</t>
+          <t>same</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>17–23 kitchen 21:30</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>too late</t>
+          <t>lunch if time</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>Kallio-scale BasBas cousin. Closed Sun–Mon.</t>
+          <t>Family-owned since 2000. The kebabpizza analogue.</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Small plates</t>
+          <t>Dal / tandoor</t>
         </is>
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>https://www.thealleyhelsinki.com/</t>
+          <t>https://ravintolamountain.com/en/home/</t>
         </is>
       </c>
       <c r="P24" s="8" t="inlineStr">
@@ -5728,33 +6235,33 @@
         </is>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Way Bakery Kallio</t>
+          <t>BasBas (Baskeri &amp; Basso)</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Bakery / wine</t>
+          <t>Bistro / natural wine</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Kallio</t>
+          <t>Punavuori</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Agricolankatu 9</t>
+          <t>Tehtaankatu 27–29 courtyard</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>neighbourhood</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -5762,49 +6269,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>No reservations</t>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Book</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>09–16</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>08–19</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>08–19</t>
+          <t>from 16:00</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>08–19</t>
+          <t>from 16:00</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>08–19 morning</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>Sourdough that can hold a Kallio morning. Not a Fazer clone.</t>
+          <t>Ingredient-led small plates. Closed Sun–Mon so Tue/Wed.</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>Bread + coffee; wine later</t>
+          <t>Share plates + wine</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>https://www.waybakery.fi/kallio</t>
+          <t>https://basbas.fi/bistro/en/</t>
         </is>
       </c>
       <c r="P25" s="8" t="inlineStr">
@@ -5819,27 +6326,27 @@
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Café Succès</t>
+          <t>Nolita</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Traditional café</t>
+          <t>Seasonal bistro / wine</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Ullanlinna</t>
+          <t>Punavuori</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Korkeavuorenkatu 2</t>
+          <t>Kankurinkatu 6</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>neighbourhood</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -5847,49 +6354,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in</t>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Book dinner</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>11–17</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>08–18</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>08–18</t>
+          <t>17–22</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>08–18</t>
+          <t>17–22</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>08–18 morning</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>1957 family café; giant cinnamon bun. Near ADM.</t>
+          <t>Closed Sun–Mon. In-house sourdough with dinner.</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>Korvapuusti</t>
+          <t>Shareable bistro</t>
         </is>
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>https://succes.fi/en/frontpage/</t>
+          <t>https://nolita.fi/en/</t>
         </is>
       </c>
       <c r="P26" s="8" t="inlineStr">
@@ -5904,27 +6411,27 @@
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Eromanga</t>
+          <t>The Alley</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Bakery / lihapiirakka</t>
+          <t>Small plates / wine</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Kaartinkaupunki</t>
+          <t>Kallio</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Pohjoinen Makasiinikatu 6</t>
+          <t>Fleminginkatu 8</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>neighbourhood</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -5932,9 +6439,9 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in</t>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Book / some walk-in</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -5944,37 +6451,37 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>07:30–15:30</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>07:30–15:30</t>
+          <t>17–23 kitchen 21:30</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>07:30–15:30</t>
+          <t>17–23 kitchen 21:30</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>07:30–15:30 if buffer</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>1946-recipe meat pie. Savoury bakery, not another bun.</t>
+          <t>Kallio-scale BasBas cousin. Closed Sun–Mon.</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>Lihapiirakka</t>
+          <t>Small plates</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>https://eromanga.fi/home/</t>
+          <t>https://www.thealleyhelsinki.com/</t>
         </is>
       </c>
       <c r="P27" s="8" t="inlineStr">
@@ -5983,28 +6490,28 @@
         </is>
       </c>
       <c r="Q27" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="52" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Kannas</t>
+          <t>Way Bakery Kallio</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Finnish port classic</t>
+          <t>Bakery / wine</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Hietalahti</t>
+          <t>Kallio</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Eerikinkatu 43</t>
+          <t>Agricolankatu 9</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -6017,49 +6524,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>Book dinner</t>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>No reservations</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>14–24 kitchen 22:30</t>
+          <t>09–16</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>16–24 kitchen 22:30</t>
+          <t>08–19</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>08–19</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>08–19</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>too late</t>
+          <t>08–19 morning</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>Since 1939; sailors/dockworkers room. Less polished than Sea Horse.</t>
+          <t>Sourdough that can hold a Kallio morning. Not a Fazer clone.</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>Finnish classics</t>
+          <t>Bread + coffee; wine later</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>https://kannas.fi/english/</t>
+          <t>https://www.waybakery.fi/kallio</t>
         </is>
       </c>
       <c r="P28" s="8" t="inlineStr">
@@ -6068,18 +6575,18 @@
         </is>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Sea Horse</t>
+          <t>Café Succès</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Classic Finnish</t>
+          <t>Traditional café</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -6089,12 +6596,12 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Kapteeninkatu 11</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>icon</t>
+          <t>Korkeavuorenkatu 2</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -6102,94 +6609,94 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>Book / walk-in</t>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>15–24</t>
+          <t>11–17</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>15–24</t>
+          <t>08–18</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>15–24</t>
+          <t>08–18</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>15–24</t>
+          <t>08–18</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>15–24 (too late to start)</t>
+          <t>08–18 morning</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>1933 institution; onion steak; near ADM</t>
+          <t>1957 family café; giant cinnamon bun. Near ADM.</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>Onion steak / Baltic herring / vorschmack</t>
+          <t>Korvapuusti</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>https://www.seahorse.fi/en/restaurant-sea-horse/</t>
+          <t>https://succes.fi/en/frontpage/</t>
         </is>
       </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>Official summer 8.6.2026+</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" ht="52" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Kosmos</t>
+          <t>Eromanga</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Helsinki classic</t>
+          <t>Bakery / lihapiirakka</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Kamppi</t>
+          <t>Kaartinkaupunki</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Kalevankatu 3</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>icon</t>
+          <t>Pohjoinen Makasiinikatu 6</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Menu printed; VERIFY</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Phone / email</t>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -6199,37 +6706,37 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>11:30–24</t>
+          <t>07:30–15:30</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>11:30–24</t>
+          <t>07:30–15:30</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>11:30–24</t>
+          <t>07:30–15:30</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>11:30–24</t>
+          <t>07:30–15:30 if buffer</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>1924; blinis, vorschmack, Baltic herring. Closed Sundays.</t>
+          <t>1946-recipe meat pie. Savoury bakery, not another bun.</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>Fried Baltic herrings 22€ on fetched menu</t>
+          <t>Lihapiirakka</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>https://kosmos.fi/en/our-food/</t>
+          <t>https://eromanga.fi/home/</t>
         </is>
       </c>
       <c r="P30" s="8" t="inlineStr">
@@ -6238,33 +6745,33 @@
         </is>
       </c>
       <c r="Q30" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" ht="52" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Kannas</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Artist restaurant</t>
+          <t>Finnish port classic</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Töölö</t>
+          <t>Hietalahti</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Eteläinen Hesperiankatu 22</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>icon</t>
+          <t>Eerikinkatu 43</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -6274,47 +6781,47 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Book dinner</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>13–22</t>
+          <t>14–24 kitchen 22:30</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>12–22</t>
+          <t>16–24 kitchen 22:30</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>12–22</t>
+          <t>same</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>12–23</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>12–23</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>Since 1932; onion steak cousin in Töölö</t>
+          <t>Since 1939; sailors/dockworkers room. Less polished than Sea Horse.</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>Classic Finnish</t>
+          <t>Finnish classics</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>https://elite.fi/en/front-page/</t>
+          <t>https://kannas.fi/english/</t>
         </is>
       </c>
       <c r="P31" s="8" t="inlineStr">
@@ -6329,27 +6836,27 @@
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Yes Yes Yes</t>
+          <t>Cella</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Vegetarian seasonal</t>
+          <t>Finnish neighbourhood classic</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Punavuori</t>
+          <t>Kallio</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Iso Roobertinkatu 1</t>
+          <t>Fleminginkatu 15</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -6359,52 +6866,52 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Walk-in / book</t>
+          <t>Call / walk-in</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>15–22</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>15–23</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>hours not yet published*</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>hours not yet published*</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>Local-farm veg; wine. Hours not on official info page.</t>
+          <t>Since 1969; non-grand Kallio classic. Official page only lists through Mon 17 Aug — VERIFY Tue–Thu.</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>Seasonal plates</t>
+          <t>Finnish pub-restaurant</t>
         </is>
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>https://yesyesyes.fi/</t>
+          <t>https://www.ravintolacella.fi/</t>
         </is>
       </c>
       <c r="P32" s="8" t="inlineStr">
         <is>
-          <t>Official address; hours VERIFY</t>
+          <t>Official through 17 Aug</t>
         </is>
       </c>
       <c r="Q32" s="8" t="n">
@@ -6414,22 +6921,22 @@
     <row r="33" ht="52" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Löyly Restaurant</t>
+          <t>Carelia</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Finnish casual / terrace</t>
+          <t>French brasserie</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Hernesaari</t>
+          <t>Taka-Töölö</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Hernesaarenranta 4</t>
+          <t>Mannerheimintie 56</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -6442,54 +6949,54 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in terrace</t>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Book</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Kitchen 11–22</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Kitchen 11–23</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>Kitchen 11–23</t>
+          <t>16–23</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>Kitchen 11–23</t>
+          <t>16–23</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>Kitchen 11–23</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>After sauna — not a destination kitchen</t>
+          <t>1920s pharmacy room. Summer break ended 12 Aug 2026. Closed Sun–Mon.</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Lohikeitto</t>
+          <t>Brasserie, not a Finnish-national menu</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>https://www.loylyhelsinki.fi/en/info</t>
+          <t>https://ravintolacarelia.fi/en/home-2/</t>
         </is>
       </c>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>Official kitchen hours</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="Q33" s="8" t="n">
@@ -6499,770 +7006,1365 @@
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Finnjävel Salonki</t>
+          <t>Harju 8</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Finnish fine dining</t>
+          <t>Bistro / natural wine</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Kamppi</t>
+          <t>Kallio</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Ainonkatu 3</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>icon</t>
+          <t>Harjutori 8</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>star-tier VERIFY</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>Book</t>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in — no reservation</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>11–late*</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>11–late*</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>17–23</t>
+          <t>11–late*</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>17–23</t>
+          <t>11–late*</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>Leave 15:00</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>Michelin; skip unless you decide to blow the budget. Summer holiday already over.</t>
+          <t>Spontaneous Kallio living room. Exact kitchen close not on MyHelsinki — VERIFY food service.</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Tasting</t>
+          <t>Wine + plates; expect a wait</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>https://finnjavel.fi/en/</t>
+          <t>https://www.myhelsinki.fi/places/harju-8/</t>
         </is>
       </c>
       <c r="P34" s="8" t="inlineStr">
         <is>
-          <t>Official hours</t>
+          <t>MyHelsinki daily 11–late</t>
         </is>
       </c>
       <c r="Q34" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" ht="52" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Olo / Palace</t>
+          <t>Lohtu</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Nordic 1–2★</t>
+          <t>Vegan hall lunch</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Harbour</t>
+          <t>Hakaniemi Market Hall 2F</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>VERIFY live</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>icon</t>
+          <t>Hämeentie 1 A</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>cheap-everyday</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>200+ VERIFY</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>Book weeks ahead</t>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in lunch</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CLOSED (hall)</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>lunch 11–15:30; porridge 08:30–10:30</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>same</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>Leave 15:00</t>
+          <t>lunch if buffer</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>Blow-budget. Skip unless you choose to.</t>
+          <t>Plant-based hall lunch. Not a dinner. Hall closed Sunday.</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>Tasting</t>
-        </is>
-      </c>
-      <c r="O35" s="8" t="inlineStr">
-        <is>
-          <t>Michelin / official sites</t>
+          <t>Vegan comfort lunch</t>
+        </is>
+      </c>
+      <c r="O35" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ravintolalohtu.fi/en/</t>
         </is>
       </c>
       <c r="P35" s="8" t="inlineStr">
         <is>
-          <t>Not fetched in full this pass</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
+          <t>Sea Horse</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Classic Finnish</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Ullanlinna</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Kapteeninkatu 11</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Book / walk-in</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>15–24</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>15–24</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>15–24</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>15–24</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>15–24 (too late to start)</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>1933 institution; onion steak; near ADM</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>Onion steak / Baltic herring / vorschmack</t>
+        </is>
+      </c>
+      <c r="O36" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seahorse.fi/en/restaurant-sea-horse/</t>
+        </is>
+      </c>
+      <c r="P36" s="8" t="inlineStr">
+        <is>
+          <t>Official summer 8.6.2026+</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" ht="52" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Kosmos</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Helsinki classic</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Kamppi</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Kalevankatu 3</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Menu printed; VERIFY</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Phone / email</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>11:30–24</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>11:30–24</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>11:30–24</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>11:30–24</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>1924; blinis, vorschmack, Baltic herring. Closed Sundays.</t>
+        </is>
+      </c>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>Fried Baltic herrings 22€ on fetched menu</t>
+        </is>
+      </c>
+      <c r="O37" s="11" t="inlineStr">
+        <is>
+          <t>https://kosmos.fi/en/our-food/</t>
+        </is>
+      </c>
+      <c r="P37" s="8" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="Q37" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" ht="52" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Artist restaurant</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Töölö</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Eteläinen Hesperiankatu 22</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>13–22</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>12–22</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>12–22</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>12–23</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>12–23</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>Since 1932; onion steak cousin in Töölö</t>
+        </is>
+      </c>
+      <c r="N38" s="8" t="inlineStr">
+        <is>
+          <t>Classic Finnish</t>
+        </is>
+      </c>
+      <c r="O38" s="11" t="inlineStr">
+        <is>
+          <t>https://elite.fi/en/front-page/</t>
+        </is>
+      </c>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" ht="52" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Yes Yes Yes</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Vegetarian seasonal</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Punavuori</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Iso Roobertinkatu 1</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>hot</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in / book</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>Local-farm veg; wine. Hours not on official info page.</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>Seasonal plates</t>
+        </is>
+      </c>
+      <c r="O39" s="11" t="inlineStr">
+        <is>
+          <t>https://yesyesyes.fi/</t>
+        </is>
+      </c>
+      <c r="P39" s="8" t="inlineStr">
+        <is>
+          <t>Official address; hours VERIFY</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" ht="52" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Löyly Restaurant</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Finnish casual / terrace</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Hernesaari</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Hernesaarenranta 4</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>neighbourhood</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in terrace</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Kitchen 11–22</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Kitchen 11–23</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Kitchen 11–23</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Kitchen 11–23</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>Kitchen 11–23</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>After sauna — not a destination kitchen</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t>Lohikeitto</t>
+        </is>
+      </c>
+      <c r="O40" s="11" t="inlineStr">
+        <is>
+          <t>https://www.loylyhelsinki.fi/en/info</t>
+        </is>
+      </c>
+      <c r="P40" s="8" t="inlineStr">
+        <is>
+          <t>Official kitchen hours</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" ht="52" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Finnjävel Salonki</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Finnish fine dining</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Kamppi</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Ainonkatu 3</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>star-tier VERIFY</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>17–23</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>17–23</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>Leave 15:00</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>Michelin; skip unless you decide to blow the budget. Summer holiday already over.</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>Tasting</t>
+        </is>
+      </c>
+      <c r="O41" s="11" t="inlineStr">
+        <is>
+          <t>https://finnjavel.fi/en/</t>
+        </is>
+      </c>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
+          <t>Official hours</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" ht="52" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Olo / Palace</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Nordic 1–2★</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Harbour</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY live</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>200+ VERIFY</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Book weeks ahead</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>Leave 15:00</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>Blow-budget. Skip unless you choose to.</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t>Tasting</t>
+        </is>
+      </c>
+      <c r="O42" s="8" t="inlineStr">
+        <is>
+          <t>Michelin / official sites</t>
+        </is>
+      </c>
+      <c r="P42" s="8" t="inlineStr">
+        <is>
+          <t>Not fetched in full this pass</t>
+        </is>
+      </c>
+      <c r="Q42" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" ht="52" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
           <t>Nepalese (Kallio)</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Nepalese</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>Kallio</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>Pick a busy room</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>cheap-everyday</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>Walk-in</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>Many open</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Many open</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Many open</t>
         </is>
       </c>
-      <c r="K36" s="8" t="inlineStr">
+      <c r="K43" s="8" t="inlineStr">
         <is>
           <t>Many open</t>
         </is>
       </c>
-      <c r="L36" s="8" t="inlineStr">
+      <c r="L43" s="8" t="inlineStr">
         <is>
           <t>Light only</t>
         </is>
       </c>
-      <c r="M36" s="8" t="inlineStr">
+      <c r="M43" s="8" t="inlineStr">
         <is>
           <t>Helsinki's kebabpizza analogue — ordinary diaspora lunch</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr">
+      <c r="N43" s="8" t="inlineStr">
         <is>
           <t>Dal bhat / momo</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O43" s="8" t="inlineStr">
         <is>
           <t>Walk Hämeentie</t>
         </is>
       </c>
-      <c r="P36" s="8" t="inlineStr">
+      <c r="P43" s="8" t="inlineStr">
         <is>
           <t>Neighbourhood observation, not a single venue</t>
         </is>
       </c>
-      <c r="Q36" s="8" t="n">
+      <c r="Q43" s="8" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="37" ht="52" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+    <row r="44" ht="52" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Savotta / Zetor / Kappeli</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>Tourist Finnish</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>Senate Square / Esplanadi</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="F37" s="12" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I37" s="12" t="inlineStr">
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J37" s="12" t="inlineStr">
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K37" s="12" t="inlineStr">
+      <c r="K44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L37" s="12" t="inlineStr">
+      <c r="L44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr">
+      <c r="M44" s="12" t="inlineStr">
         <is>
           <t>Postcard Finland</t>
         </is>
       </c>
-      <c r="N37" s="12" t="inlineStr">
+      <c r="N44" s="12" t="inlineStr">
         <is>
           <t>Don't</t>
         </is>
       </c>
-      <c r="O37" s="12" t="inlineStr">
+      <c r="O44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P37" s="12" t="inlineStr">
+      <c r="P44" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q37" s="12" t="n">
+      <c r="Q44" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="52" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+    <row r="45" ht="52" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Sushi buffet chains</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>Buffet</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>Everywhere</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I38" s="12" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J38" s="12" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K38" s="12" t="inlineStr">
+      <c r="K45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L38" s="12" t="inlineStr">
+      <c r="L45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr">
+      <c r="M45" s="12" t="inlineStr">
         <is>
           <t>Not Domo</t>
         </is>
       </c>
-      <c r="N38" s="12" t="inlineStr">
+      <c r="N45" s="12" t="inlineStr">
         <is>
           <t>Don't</t>
         </is>
       </c>
-      <c r="O38" s="12" t="inlineStr">
+      <c r="O45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P38" s="12" t="inlineStr">
+      <c r="P45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q38" s="12" t="n">
+      <c r="Q45" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="52" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="46" ht="52" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Momotoko</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>Ramen CLOSED</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>Yliopistonkatu 5 (former)</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H46" s="12" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="J39" s="12" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="K39" s="12" t="inlineStr">
+      <c r="K46" s="12" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="L39" s="12" t="inlineStr">
+      <c r="L46" s="12" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="M39" s="12" t="inlineStr">
+      <c r="M46" s="12" t="inlineStr">
         <is>
           <t>Cathywong Oy bankruptcy May 2025; chain said permanently closed</t>
         </is>
       </c>
-      <c r="N39" s="12" t="inlineStr">
+      <c r="N46" s="12" t="inlineStr">
         <is>
           <t>Do not go</t>
         </is>
       </c>
-      <c r="O39" s="14" t="inlineStr">
+      <c r="O46" s="14" t="inlineStr">
         <is>
           <t>https://www.hs.fi/helsinki/art-2000011230551.html</t>
         </is>
       </c>
-      <c r="P39" s="12" t="inlineStr">
+      <c r="P46" s="12" t="inlineStr">
         <is>
           <t>HS 15.5.2025 + MTV 31.5.2025</t>
         </is>
       </c>
-      <c r="Q39" s="12" t="n">
+      <c r="Q46" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="40" ht="52" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
+    <row r="47" ht="52" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Wino</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Wine bar CLOSED this trip</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>Fleminginkatu 11</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="F40" s="12" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>CLOSED 1.6–3.9.2026</t>
         </is>
       </c>
-      <c r="I40" s="12" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="J40" s="12" t="inlineStr">
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="K40" s="12" t="inlineStr">
+      <c r="K47" s="12" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="L40" s="12" t="inlineStr">
+      <c r="L47" s="12" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr">
+      <c r="M47" s="12" t="inlineStr">
         <is>
           <t>Facade renovation. Do not go.</t>
         </is>
       </c>
-      <c r="N40" s="12" t="inlineStr">
+      <c r="N47" s="12" t="inlineStr">
         <is>
           <t>Don't</t>
         </is>
       </c>
-      <c r="O40" s="14" t="inlineStr">
+      <c r="O47" s="14" t="inlineStr">
         <is>
           <t>https://www.wino.fi/restaurant-wino/</t>
         </is>
       </c>
-      <c r="P40" s="12" t="inlineStr">
+      <c r="P47" s="12" t="inlineStr">
         <is>
           <t>Official closure notice</t>
         </is>
       </c>
-      <c r="Q40" s="12" t="n">
+      <c r="Q47" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="52" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
+    <row r="48" ht="52" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>Restaurant Kuu</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Töölö classic CLOSED</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>Töölönkatu 27</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H41" s="12" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>CLOSED from 1.7.2026</t>
         </is>
       </c>
-      <c r="I41" s="12" t="inlineStr">
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="J41" s="12" t="inlineStr">
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="K41" s="12" t="inlineStr">
+      <c r="K48" s="12" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="L41" s="12" t="inlineStr">
+      <c r="L48" s="12" t="inlineStr">
         <is>
           <t>same</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr">
+      <c r="M48" s="12" t="inlineStr">
         <is>
           <t>Housing-company renovation; reopen autumn. Don't google-walk there.</t>
         </is>
       </c>
-      <c r="N41" s="12" t="inlineStr">
+      <c r="N48" s="12" t="inlineStr">
         <is>
           <t>Don't</t>
         </is>
       </c>
-      <c r="O41" s="14" t="inlineStr">
+      <c r="O48" s="14" t="inlineStr">
         <is>
           <t>https://ravintolakuu.fi/en/kuu-closed-from-1-7/</t>
         </is>
       </c>
-      <c r="P41" s="12" t="inlineStr">
+      <c r="P48" s="12" t="inlineStr">
         <is>
           <t>Official</t>
         </is>
       </c>
-      <c r="Q41" s="12" t="n">
+      <c r="Q48" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="52" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+    <row r="49" ht="52" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>Adzika / Satkar / Sandro</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Moved or dead names</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>stale maps</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>skip</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H42" s="12" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>TRAP</t>
         </is>
       </c>
-      <c r="I42" s="12" t="inlineStr">
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>TRAP</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>TRAP</t>
         </is>
       </c>
-      <c r="K42" s="12" t="inlineStr">
+      <c r="K49" s="12" t="inlineStr">
         <is>
           <t>TRAP</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="L49" s="12" t="inlineStr">
         <is>
           <t>TRAP</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr">
+      <c r="M49" s="12" t="inlineStr">
         <is>
           <t>Adzika seeking premises; Satkar is now Sansar; Sandro closed 28 Feb.</t>
         </is>
       </c>
-      <c r="N42" s="12" t="inlineStr">
+      <c r="N49" s="12" t="inlineStr">
         <is>
           <t>Search current names</t>
         </is>
       </c>
-      <c r="O42" s="12" t="inlineStr">
+      <c r="O49" s="12" t="inlineStr">
         <is>
           <t>See research/neighbourhood-eateries.md</t>
         </is>
       </c>
-      <c r="P42" s="12" t="inlineStr">
+      <c r="P49" s="12" t="inlineStr">
         <is>
           <t>Official closure pages</t>
         </is>
       </c>
-      <c r="Q42" s="12" t="n">
+      <c r="Q49" s="12" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q42"/>
+  <autoFilter ref="A1:Q49"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -7276,9 +8378,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId18"/>
@@ -7295,9 +8397,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7310,7 +8419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7473,116 +8582,153 @@
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3b</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Gaijin, Bulevardi 6</t>
+          <t>Café Story, Vanha Kauppahalli</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Next to Ekberg — NOT brunch</t>
+          <t>~15–20 min via harbour</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Dinner from 15:00 Sun; lunch closed through 17.8.2026</t>
+          <t>Sun 10–17, kitchen 10–16 official</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Park for 15:00 if Ekberg was too light</t>
+          <t>Salmon soup in the old market hall — harbour orientation, more tourist-facing than Ekberg</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Book gaijin.fi</t>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>You insist on eating at 11:30</t>
+          <t>You want Design District not the postcard harbour</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Café Regatta, Töölö shore</t>
+          <t>Gaijin, Bulevardi 6</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>TOO FAR (~40 min) for arrival</t>
+          <t>Next to Ekberg — NOT brunch</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>Dinner from 15:00 Sun; lunch closed through 17.8.2026</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Cute; save for a Töölö walk another day</t>
+          <t>Park for 15:00 if Ekberg was too light</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Book gaijin.fi</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>You are tired from the ship</t>
+          <t>You insist on eating at 11:30</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Café Regatta, Töölö shore</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>TOO FAR (~40 min) for arrival</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Cute; save for a Töölö walk another day</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>You are tired from the ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Terminal / leftover fruit</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>0 min</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Emergency only</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>You want Helsinki to begin well</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
   </hyperlinks>
@@ -7597,7 +8743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7990,131 +9136,131 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Temppeliaukio</t>
+          <t>Kulttuurisauna</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>Quiet public sauna</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>90 min</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Door ticket</t>
+          <t>Book evenings (calendar ~2 weeks)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Hours change with services; check the week. Sunday 10:00 is worship, not sightseeing.</t>
+          <t>Eve Wed–Sun 16–20; morning walk-in Fri–Sun 8–11:30. First-timers: come alone. No groups &gt;2. Hakaniemenranta 17.</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>https://www.temppeliaukiochurch.fi/en/index/nimi.html</t>
+          <t>https://www.kulttuurisauna.fi/</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Photo only</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Quieter Löyly alternative</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Backup Wed</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Adult €8 official</t>
+          <t>Adult €17 official; student €13. Bring own towel.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Helsinki Cathedral / Senate Square</t>
+          <t>Aalto House</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Postcard</t>
+          <t>Architecture tour</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>15 min pass-through</t>
+          <t>1 h</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Guided only; book shop.alvaraalto.fi</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>On the walk from harbour — not a day</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Jul–Aug Tue–Fri 11–16 hourly; Sat–Sun 12–16. Closed Mon. Max 15. Riihitie 20, Munkkiniemi.</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>https://www.alvaraalto.fi/en/location/the-aalto-house/</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Orientation only</t>
+          <t>Aalto, not a drop-in museum</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Pass by</t>
+          <t>Optional Tue morning</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>€32 / students €16 official</t>
         </is>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Seurasaari</t>
+          <t>Temppeliaukio</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Open-air museum</t>
+          <t>Church</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>half day</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Door ticket</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Skansen analogue — you skipped Skansen</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Hours change with services; check the week. Sunday 10:00 is worship, not sightseeing.</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>https://www.temppeliaukiochurch.fi/en/index/nimi.html</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Skip this trip</t>
+          <t>Photo only</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -8124,59 +9270,153 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Adult €8 official</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
+          <t>Helsinki Cathedral / Senate Square</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Postcard</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>15 min pass-through</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>On the walk from harbour — not a day</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Orientation only</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Pass by</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Seurasaari</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Open-air museum</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>half day</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Skansen analogue — you skipped Skansen</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Skip this trip</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
           <t>Night of the Arts</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>City-wide</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>evening 20 Aug</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Many free</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Confirmed Thu 20 Aug 2026. You leave 15:00.</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>https://helsinkifestival.fi/taiteidenyo/en/instructions-for-event-organisers/</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>FOMO only</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Miss</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A1:I14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -8186,7 +9426,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8521,7 +9763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8906,44 +10148,44 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Sea Horse</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 15–24</t>
+          <t>Skörd</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED*</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>OPEN 15–24</t>
+          <t>OPEN dinner*</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>OPEN 15–24</t>
+          <t>OPEN dinner*</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>OPEN 15–24</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>OPEN but leaving</t>
+          <t>OPEN dinner*</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Official summer</t>
+          <t>Official 86e/72e; hours Time Out Mon–Sat</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Kosmos</t>
+          <t>Kuurna</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
@@ -8953,22 +10195,22 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11:30–24</t>
+          <t>OPEN 17–23</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN 17–23</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>OPEN morning/lunch</t>
+          <t>OPEN 17–23</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -8980,91 +10222,91 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Sea Horse</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>OPEN 13–22</t>
+          <t>OPEN 15–24</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>OPEN 12–22</t>
+          <t>OPEN 15–24</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN 15–24</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN 15–24</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>OPEN morning</t>
+          <t>OPEN but leaving</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official summer</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Katana Ramen</t>
+          <t>Kosmos</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>CLOSED?*</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–21*</t>
+          <t>OPEN 11:30–24</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>OPEN*</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>OPEN*</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>OPEN* morning</t>
+          <t>OPEN morning/lunch</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Falstaff — VERIFY</t>
+          <t>Official</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Bui Ramen</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>OPEN 12–20</t>
+          <t>OPEN 13–22</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–21</t>
+          <t>OPEN 12–22</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -9084,150 +10326,150 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Official — not central</t>
+          <t>Official</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Amos Rex</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 11–17</t>
+          <t>Katana Ramen</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED?*</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–20</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
+          <t>OPEN 11–21*</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>OPEN*</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–20</t>
+          <t>OPEN*</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–23 (you miss evening)</t>
+          <t>OPEN* morning</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Falstaff — VERIFY</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>Bui Ramen</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–18</t>
+          <t>OPEN 12–20</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–20</t>
+          <t>OPEN 11–21</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–20</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–20</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–22 (you miss evening)</t>
+          <t>OPEN morning</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official — not central</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Oodi</t>
+          <t>Sansar</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>OPEN 10–20</t>
+          <t>OPEN 12–21</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>OPEN 8–21</t>
+          <t>OPEN 10:30–21</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>OPEN 8–21</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>OPEN 8–21</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 8–21 morning</t>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>lunch if time</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official — search Sansar not Satkar</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Löyly sauna</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 11–21</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 12–22</t>
+          <t>BasBas</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>OPEN 12–22</t>
+          <t>OPEN from 16:00</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>OPEN 9–11 &amp; 13–22</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 12–22 morning?</t>
+          <t>OPEN from 16:00</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -9239,79 +10481,375 @@
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Ateneum</t>
+          <t>Cella</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>OPEN 10–17</t>
+          <t>OPEN 15–22</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–17</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 10–18</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 10–20</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>FREE 10–20</t>
+          <t>OPEN 15–23</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Official; free day 20 Aug</t>
+          <t>Official only through 17 Aug</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>Carelia</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 16–23</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 16–23</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Official; summer break ended 12 Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Harju 8</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–late*</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>OPEN*</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>OPEN*</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>OPEN*</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>MyHelsinki — kitchen VERIFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Lohtu</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED (hall)</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>OPEN lunch 11–15:30</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>OPEN lunch</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>OPEN lunch</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>lunch if buffer</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Official; hall closed Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Amos Rex</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–17</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–20</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–20</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–23 (you miss evening)</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–18</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–20</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–20</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–20</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–22 (you miss evening)</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Oodi</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 10–20</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 8–21</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 8–21</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 8–21</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 8–21 morning</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Löyly sauna</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–21</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 12–22</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 12–22</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 9–11 &amp; 13–22</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 12–22 morning?</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Ateneum</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 10–17</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–17</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 10–18</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 10–20</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>FREE 10–20</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Official; free day 20 Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
           <t>Momotoko</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F29" s="18" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>HS/MTV 2025</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9373,7 +10911,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Allas; or hotel sauna if any</t>
+          <t>Kulttuurisauna €17/90 min Wed–Sun 16–20 (book ~2 weeks, first-timers alone); or Allas</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">

--- a/docs/helsinki-aug-2026/Helsinki-16-20-Aug-2026.xlsx
+++ b/docs/helsinki-aug-2026/Helsinki-16-20-Aug-2026.xlsx
@@ -22,14 +22,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_Itinerary'!$A$1:$J$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_Book_tonight'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Restaurants'!$A$1:$Q$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Restaurants'!$A$1:$Q$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_Arrival_brunch'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Activities'!$A$1:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_Tours_bookable'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_Open_matrix'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_Open_matrix'!$A$1:$G$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_Rain_and_skip'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_Viz_data'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_Sources'!$A$1:$E$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_Sources'!$A$1:$E$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1449,7 +1449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Shii concept + phone</t>
+          <t>Shii menu 98e; hours omitted</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>https://shii.fi/</t>
+          <t>https://shii.fi/menu</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1941,24 +1941,24 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>High concept; hours missing</t>
+          <t>High price; weekly hours VERIFY in booker</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>S-seahorse</t>
+          <t>S-hanayagi</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Sea Horse summer hours</t>
+          <t>Hanayagi 150e + TableOnline hours</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>https://www.seahorse.fi/en/restaurant-sea-horse/</t>
+          <t>https://hanayagi-omakase.com/about</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1968,24 +1968,24 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>High — official</t>
+          <t>High concept; hours from booker</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>S-kosmos</t>
+          <t>S-domo</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Kosmos hours + menu</t>
+          <t>Domo hours</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>https://kosmos.fi/en/our-food/</t>
+          <t>http://www.domoravintola.fi/</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -2002,17 +2002,17 @@
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>S-elite</t>
+          <t>S-lia</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Elite hours</t>
+          <t>Lia hours (Mon conflict)</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>https://elite.fi/en/front-page/</t>
+          <t>https://www.ravintolalia.fi/en-gb/helsinki</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2022,24 +2022,24 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>High — official</t>
+          <t>High venue; Monday pages conflict</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>S-bui</t>
+          <t>S-olo</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Bui Ramen hours + prices</t>
+          <t>Olo hours + 189e / 109e</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>https://buiramen.fi/</t>
+          <t>https://olo-ravintola.fi/en/info/</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -2056,17 +2056,17 @@
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>S-levain</t>
+          <t>S-palace</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Levain branch hours</t>
+          <t>Palace 250e menu</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>https://www.levain.fi/reservation</t>
+          <t>https://palacerestaurant.fi/en/menu</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2083,17 +2083,17 @@
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>S-loyly</t>
+          <t>S-seahorse</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Löyly sauna price + rules</t>
+          <t>Sea Horse summer hours</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>https://www.loylyhelsinki.fi/en/public-sauna</t>
+          <t>https://www.seahorse.fi/en/restaurant-sea-horse/</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -2110,17 +2110,17 @@
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>S-loyly-h</t>
+          <t>S-kosmos</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Löyly weekly hours</t>
+          <t>Kosmos hours + menu</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>https://www.loylyhelsinki.fi/en/info</t>
+          <t>https://kosmos.fi/en/our-food/</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2137,17 +2137,17 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>S-rex</t>
+          <t>S-elite</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Amos Rex hours</t>
+          <t>Elite hours</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>https://amosrex.fi/en/visit-us/</t>
+          <t>https://elite.fi/en/front-page/</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -2164,17 +2164,17 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>S-rex-t</t>
+          <t>S-bui</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Amos Rex tickets</t>
+          <t>Bui Ramen hours + prices</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>https://amosrex.fi/en/tickets/</t>
+          <t>https://buiramen.fi/</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2191,17 +2191,17 @@
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>S-adm</t>
+          <t>S-levain</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>ADM hours + construction</t>
+          <t>Levain branch hours</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>https://admuseo.fi/en/visit-us/</t>
+          <t>https://www.levain.fi/reservation</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2218,17 +2218,17 @@
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>S-oodi</t>
+          <t>S-loyly</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Oodi hours 2026</t>
+          <t>Löyly sauna price + rules</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>https://oodihelsinki.fi/en/arrival/</t>
+          <t>https://www.loylyhelsinki.fi/en/public-sauna</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -2245,17 +2245,17 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>S-hsl</t>
+          <t>S-loyly-h</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>HSL Suomenlinna ferry</t>
+          <t>Löyly weekly hours</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>https://www.hsl.fi/en/travelling/visitors/suomenlinna</t>
+          <t>https://www.loylyhelsinki.fi/en/info</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -2265,24 +2265,24 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>High — official; fare can move</t>
+          <t>High — official</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>S-sl-arr</t>
+          <t>S-rex</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Suomenlinna arriving</t>
+          <t>Amos Rex hours</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>https://suomenlinna.fi/en/explore/arriving/</t>
+          <t>https://amosrex.fi/en/visit-us/</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2299,17 +2299,17 @@
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>S-sl-tour</t>
+          <t>S-rex-t</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>English guided tour 2026</t>
+          <t>Amos Rex tickets</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>https://suomenlinna.johku.com/en_US/liput/guided-walking-tour-in-english</t>
+          <t>https://amosrex.fi/en/tickets/</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -2319,24 +2319,24 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>High schedule; inventory unknown</t>
+          <t>High — official</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>S-ateneum</t>
+          <t>S-adm</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Ateneum hours + free 20 Aug</t>
+          <t>ADM hours + construction</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>https://ateneum.fi/en/opening-hours-and-tickets/</t>
+          <t>https://admuseo.fi/en/visit-us/</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>S-allas</t>
+          <t>S-oodi</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Allas hours</t>
+          <t>Oodi hours 2026</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>https://allasseapool.fi/en/</t>
+          <t>https://oodihelsinki.fi/en/arrival/</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -2380,44 +2380,44 @@
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>S-momo</t>
+          <t>S-hsl</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Momotoko bankruptcy</t>
+          <t>HSL Suomenlinna ferry</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>https://www.hs.fi/helsinki/art-2000011230551.html</t>
+          <t>https://www.hsl.fi/en/travelling/visitors/suomenlinna</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>High — local press, closure status</t>
+          <t>High — official; fare can move</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>S-katana</t>
+          <t>S-sl-arr</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Katana hours (Falstaff)</t>
+          <t>Suomenlinna arriving</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>https://www.falstaff.com/at/streetfood/katana-ramen-restaurant</t>
+          <t>https://suomenlinna.fi/en/explore/arriving/</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2427,24 +2427,24 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Medium — secondary, no official hours page</t>
+          <t>High — official</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>S-sansar</t>
+          <t>S-sl-tour</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Sansar hours (ex-Satkar)</t>
+          <t>English guided tour 2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>https://www.sansar.fi/</t>
+          <t>https://suomenlinna.johku.com/en_US/liput/guided-walking-tour-in-english</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -2454,24 +2454,24 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>High — official</t>
+          <t>High schedule; inventory unknown</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>S-mountain</t>
+          <t>S-ateneum</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Restaurant Mountain hours</t>
+          <t>Ateneum hours + free 20 Aug</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>https://ravintolamountain.com/en/home/</t>
+          <t>https://ateneum.fi/en/opening-hours-and-tickets/</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2488,17 +2488,17 @@
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>S-basbas</t>
+          <t>S-allas</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>BasBas hours</t>
+          <t>Allas hours</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>https://basbas.fi/bistro/en/</t>
+          <t>https://allasseapool.fi/en/</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -2515,44 +2515,44 @@
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>S-cella</t>
+          <t>S-momo</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Cella hours through 17 Aug</t>
+          <t>Momotoko bankruptcy</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>https://www.ravintolacella.fi/</t>
+          <t>https://www.hs.fi/helsinki/art-2000011230551.html</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>High Sun–Mon; Tue–Thu unverified</t>
+          <t>High — local press, closure status</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>S-carelia</t>
+          <t>S-katana</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Carelia hours + 2026 summer break</t>
+          <t>Katana hours (Falstaff)</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>https://ravintolacarelia.fi/en/home-2/</t>
+          <t>https://www.falstaff.com/at/streetfood/katana-ramen-restaurant</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2562,24 +2562,24 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>High — official</t>
+          <t>Medium — secondary, no official hours page</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>S-harju8</t>
+          <t>S-sansar</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Harju 8 listing</t>
+          <t>Sansar hours (ex-Satkar)</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>https://www.myhelsinki.fi/places/harju-8/</t>
+          <t>https://www.sansar.fi/</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2589,24 +2589,24 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Medium — MyHelsinki; kitchen close missing</t>
+          <t>High — official</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>S-lohtu</t>
+          <t>S-mountain</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Lohtu hall lunch hours</t>
+          <t>Restaurant Mountain hours</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>https://www.ravintolalohtu.fi/en/</t>
+          <t>https://ravintolamountain.com/en/home/</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -2623,32 +2623,167 @@
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
+          <t>S-basbas</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>BasBas hours</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>https://basbas.fi/bistro/en/</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>S-cella</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Cella hours through 17 Aug</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ravintolacella.fi/</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>High Sun–Mon; Tue–Thu unverified</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>S-carelia</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Carelia hours + 2026 summer break</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>https://ravintolacarelia.fi/en/home-2/</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>S-harju8</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Harju 8 listing</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>https://www.myhelsinki.fi/places/harju-8/</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Medium — MyHelsinki; kitchen close missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>S-lohtu</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Lohtu hall lunch hours</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ravintolalohtu.fi/en/</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>High — official</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
           <t>S-nbhd</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Neighbourhood eateries research (40 venues)</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>docs/helsinki-aug-2026/research/neighbourhood-eateries.md</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>Compiled from official/MyHelsinki/HS — VERIFY live</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E44"/>
+  <autoFilter ref="A1:E49"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -2692,6 +2827,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3864,17 +4004,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Wed 19 (closed Sun–Tue)</t>
+          <t>Wed 19 (closed Sun–Tue official)</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Call / site</t>
+          <t>Call / site — no walk-ins</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>https://www.latitude25.fi/</t>
+          <t>https://www.latitude25.fi/booking/</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -3884,12 +4024,12 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Shii https://shii.fi/ 050 329 0360</t>
+          <t>Shii €98 — hours VERIFY in DinnerBooking, not assumed Sun–Tue closed</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Only if Grön fails and you want omakase</t>
+          <t>Only if Grön/Skörd fail and you want omakase</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5501,34 +5641,34 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
+          <t>98e menu official</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Book DinnerBooking</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Book</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
           <t>Leave 15:00</t>
@@ -5536,22 +5676,22 @@
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>16 seats; 11-course; cannot be made vegetarian</t>
+          <t>11-course. Cannot be vegetarian. Do NOT copy Latitude's Sun–Tue closure onto Shii.</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>Counter</t>
+          <t>Omakase; sake pairing 62e official</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>https://shii.fi/</t>
+          <t>https://shii.fi/menu</t>
         </is>
       </c>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>Official concept; hours missing — VERIFY</t>
+          <t>Official menu/price; weekly hours not published — VERIFY in booker</t>
         </is>
       </c>
       <c r="Q16" s="8" t="n">
@@ -5561,82 +5701,82 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Domo</t>
+          <t>Hanayagi Omakase</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Sushi à la carte</t>
+          <t>Aged sushi omakase</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Kamppi</t>
+          <t>Kaartinkaupunki</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Kalevankatu 21</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>neighbourhood</t>
+          <t>Kasarmikatu 25</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>150e course official booker</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Walk-in / call</t>
+          <t>Reservation only</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CLOSED*</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CLOSED*</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>18:00–20:30*</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>18:00–20:30*</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>Long-running; more fish less rice; not buffet</t>
+          <t>Eight seats. Tuesday sushi alternative if Nolla is full. Hours from TableOnline — VERIFY.</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>Nigiri</t>
-        </is>
-      </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>VERIFY official site</t>
+          <t>Omakase</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tableonline.fi/en/helsinki/hanayagi-omakase/1689/book</t>
         </is>
       </c>
       <c r="P17" s="8" t="inlineStr">
         <is>
-          <t>Hours not captured — VERIFY</t>
+          <t>TableOnline hours; official concept page</t>
         </is>
       </c>
       <c r="Q17" s="8" t="n">
@@ -5646,177 +5786,177 @@
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Katana Ramen</t>
+          <t>Domo</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Ramen</t>
+          <t>Sushi à la carte</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Punavuori / Telakka</t>
+          <t>Kamppi</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Telakkakatu 12</t>
+          <t>Kalevankatu 21</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>VERIFY (2024 PDFs stale)</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Walk-in</t>
+          <t>Email / phone</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>CLOSED?*</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>11–21*</t>
+          <t>11–14:30 &amp; 17–21</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>11–21*</t>
+          <t>same</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>11–21*</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>11–21*</t>
+          <t>lunch if buffer</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>Dedicated ramen after Momotoko died. HS reviewed Jul 2026.</t>
+          <t>À la carte, not buffet. July 2026 local coverage confirms it is active.</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>Tonkotsu</t>
-        </is>
-      </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>katanaramenclub@gmail.com</t>
+          <t>Nigiri / bento</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>http://www.domoravintola.fi/</t>
         </is>
       </c>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t>Falstaff hours (secondary)</t>
+          <t>Official hours</t>
         </is>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Bui Ramen</t>
+          <t>Restaurant Lia</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Ramen / mazemen</t>
+          <t>Modern Georgian</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Kalasatama</t>
+          <t>Erottaja</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Aallonhalkoja 1 L T 2</t>
+          <t>Erottajankatu 2 (enter Uudenmaankatu)</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>neighbourhood</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Bui Paitan 17.90€ official</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in / book</t>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Book / call</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>12–20</t>
+          <t>15–22</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>CLOSED?*</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>16–22</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>Handmade noodles; not central — only if east</t>
+          <t>Georgian backup. Official pages conflict on Monday; contact page says open, venue page says Mon–Tue closed.</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>Bui Paitan</t>
+          <t>Khachapuri / supra</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>https://buiramen.fi/</t>
+          <t>https://www.ravintolalia.fi/en-gb/helsinki</t>
         </is>
       </c>
       <c r="P19" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official pages conflict Mon — VERIFY</t>
         </is>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Ramen Ichiraku</t>
+          <t>Katana Ramen</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -5826,17 +5966,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Kamppi mall 5F</t>
+          <t>Punavuori / Telakka</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Urho Kekkosen katu 1</t>
+          <t>Telakkakatu 12</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>cheap-everyday</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -5851,72 +5991,72 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>12–19</t>
+          <t>CLOSED?*</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>11–21*</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>11–21*</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>11–21</t>
+          <t>11–21*</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>11–21 morning</t>
+          <t>11–21*</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>Emergency bowl. Mall. Time Out: reliable, not soulful.</t>
+          <t>Dedicated ramen after Momotoko died. HS reviewed Jul 2026. Sunday omitted on Falstaff — not an official closure.</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Tonkotsu / tan tan</t>
-        </is>
-      </c>
-      <c r="O20" s="11" t="inlineStr">
-        <is>
-          <t>https://www.kamppihelsinki.fi/en/shops-and-services/other-stores/ramen-ichiraku/-/110</t>
+          <t>Tonkotsu</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>katanaramenclub@gmail.com</t>
         </is>
       </c>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>Official Kamppi listing</t>
+          <t>Falstaff hours (secondary)</t>
         </is>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Sushi Wagocoro</t>
+          <t>Bui Ramen</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Sushi neighbourhood</t>
+          <t>Ramen / mazemen</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Taka-Töölö</t>
+          <t>Kalasatama</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Runeberginkatu 63 A 21</t>
+          <t>Aallonhalkoja 1 L T 2</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -5926,87 +6066,87 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>Book/call — tiny</t>
+          <t>Bui Paitan 17.90€ official</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in / book</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>12–20</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>Japanese-owned small room. Confirm before crossing town.</t>
+          <t>Handmade noodles; not central — only if east</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>Nigiri</t>
+          <t>Bui Paitan</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>https://www.myhelsinki.fi/places/sushi-wagocoro/</t>
+          <t>https://buiramen.fi/</t>
         </is>
       </c>
       <c r="P21" s="8" t="inlineStr">
         <is>
-          <t>MyHelsinki — hours VERIFY</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Kabuki</t>
+          <t>Ramen Ichiraku</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Traditional Japanese</t>
+          <t>Ramen</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Kamppi</t>
+          <t>Kamppi mall 5F</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Lapinlahdenkatu 12</t>
+          <t>Urho Kekkosen katu 1</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>neighbourhood</t>
+          <t>cheap-everyday</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -6014,84 +6154,84 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>Book — small room</t>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>12–19</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11–21 morning</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>Old-school Japanese / tatami, not Nordic omakase theatre</t>
+          <t>Emergency bowl. Mall. Time Out: reliable, not soulful.</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Sushi / set</t>
+          <t>Tonkotsu / tan tan</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>https://www.myhelsinki.fi/places/kabuki/</t>
+          <t>https://www.kamppihelsinki.fi/en/shops-and-services/other-stores/ramen-ichiraku/-/110</t>
         </is>
       </c>
       <c r="P22" s="8" t="inlineStr">
         <is>
-          <t>MyHelsinki — hours VERIFY</t>
+          <t>Official Kamppi listing</t>
         </is>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Sansar (ex-Satkar)</t>
+          <t>Sushi Wagocoro</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Nepalese</t>
+          <t>Sushi neighbourhood</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Kamppi</t>
+          <t>Taka-Töölö</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Fredrikinkatu 46</t>
+          <t>Runeberginkatu 63 A 21</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>cheap-everyday</t>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -6099,84 +6239,84 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in lunch</t>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Book/call — tiny</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>12–21</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>10:30–21; lunch to 16</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>lunch if time</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>Kamppi since 1998. Ordinary diaspora lunch. Search Sansar, not Satkar.</t>
+          <t>Japanese-owned small room. Confirm before crossing town.</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>Tandoor / curry lunch</t>
+          <t>Nigiri</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>https://www.sansar.fi/</t>
+          <t>https://www.myhelsinki.fi/places/sushi-wagocoro/</t>
         </is>
       </c>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>MyHelsinki — hours VERIFY</t>
         </is>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Restaurant Mountain</t>
+          <t>Kabuki</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Nepalese</t>
+          <t>Traditional Japanese</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Taka-Töölö</t>
+          <t>Kamppi</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nordenskiöldinkatu 8</t>
+          <t>Lapinlahdenkatu 12</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>cheap-everyday</t>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -6184,84 +6324,84 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in lunch</t>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Book — small room</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>12:30–22</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>10:30–22:30; lunch to 15</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>lunch if time</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>Family-owned since 2000. The kebabpizza analogue.</t>
+          <t>Old-school Japanese / tatami, not Nordic omakase theatre</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Dal / tandoor</t>
+          <t>Sushi / set</t>
         </is>
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>https://ravintolamountain.com/en/home/</t>
+          <t>https://www.myhelsinki.fi/places/kabuki/</t>
         </is>
       </c>
       <c r="P24" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>MyHelsinki — hours VERIFY</t>
         </is>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>BasBas (Baskeri &amp; Basso)</t>
+          <t>Sansar (ex-Satkar)</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Bistro / natural wine</t>
+          <t>Nepalese</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Punavuori</t>
+          <t>Kamppi</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Tehtaankatu 27–29 courtyard</t>
+          <t>Fredrikinkatu 46</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>cheap-everyday</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -6269,49 +6409,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>Book</t>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in lunch</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>12–21</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>10:30–21; lunch to 16</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>from 16:00</t>
+          <t>same</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>from 16:00</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>too late</t>
+          <t>lunch if time</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>Ingredient-led small plates. Closed Sun–Mon so Tue/Wed.</t>
+          <t>Kamppi since 1998. Ordinary diaspora lunch. Search Sansar, not Satkar.</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>Share plates + wine</t>
+          <t>Tandoor / curry lunch</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>https://basbas.fi/bistro/en/</t>
+          <t>https://www.sansar.fi/</t>
         </is>
       </c>
       <c r="P25" s="8" t="inlineStr">
@@ -6326,27 +6466,27 @@
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Nolita</t>
+          <t>Restaurant Mountain</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Seasonal bistro / wine</t>
+          <t>Nepalese</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Punavuori</t>
+          <t>Taka-Töölö</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Kankurinkatu 6</t>
+          <t>Nordenskiöldinkatu 8</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>cheap-everyday</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -6354,49 +6494,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>Book dinner</t>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in lunch</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>12:30–22</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>10:30–22:30; lunch to 15</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>17–22</t>
+          <t>same</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>17–22</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>too late</t>
+          <t>lunch if time</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>Closed Sun–Mon. In-house sourdough with dinner.</t>
+          <t>Family-owned since 2000. The kebabpizza analogue.</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>Shareable bistro</t>
+          <t>Dal / tandoor</t>
         </is>
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>https://nolita.fi/en/</t>
+          <t>https://ravintolamountain.com/en/home/</t>
         </is>
       </c>
       <c r="P26" s="8" t="inlineStr">
@@ -6405,28 +6545,28 @@
         </is>
       </c>
       <c r="Q26" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>The Alley</t>
+          <t>BasBas (Baskeri &amp; Basso)</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Small plates / wine</t>
+          <t>Bistro / natural wine</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Kallio</t>
+          <t>Punavuori</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Fleminginkatu 8</t>
+          <t>Tehtaankatu 27–29 courtyard</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -6441,7 +6581,7 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Book / some walk-in</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -6456,12 +6596,12 @@
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>17–23 kitchen 21:30</t>
+          <t>from 16:00</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>17–23 kitchen 21:30</t>
+          <t>from 16:00</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
@@ -6471,17 +6611,17 @@
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>Kallio-scale BasBas cousin. Closed Sun–Mon.</t>
+          <t>Ingredient-led small plates. Closed Sun–Mon so Tue/Wed.</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>Small plates</t>
+          <t>Share plates + wine</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>https://www.thealleyhelsinki.com/</t>
+          <t>https://basbas.fi/bistro/en/</t>
         </is>
       </c>
       <c r="P27" s="8" t="inlineStr">
@@ -6490,33 +6630,33 @@
         </is>
       </c>
       <c r="Q27" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" ht="52" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Way Bakery Kallio</t>
+          <t>Nolita</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Bakery / wine</t>
+          <t>Seasonal bistro / wine</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Kallio</t>
+          <t>Punavuori</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Agricolankatu 9</t>
+          <t>Kankurinkatu 6</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>neighbourhood</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -6524,49 +6664,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>No reservations</t>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Book dinner</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>09–16</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>08–19</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>08–19</t>
+          <t>17–22</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>08–19</t>
+          <t>17–22</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>08–19 morning</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>Sourdough that can hold a Kallio morning. Not a Fazer clone.</t>
+          <t>Closed Sun–Mon. In-house sourdough with dinner.</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>Bread + coffee; wine later</t>
+          <t>Shareable bistro</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>https://www.waybakery.fi/kallio</t>
+          <t>https://nolita.fi/en/</t>
         </is>
       </c>
       <c r="P28" s="8" t="inlineStr">
@@ -6575,33 +6715,33 @@
         </is>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Café Succès</t>
+          <t>The Alley</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Traditional café</t>
+          <t>Small plates / wine</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Ullanlinna</t>
+          <t>Kallio</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Korkeavuorenkatu 2</t>
+          <t>Fleminginkatu 8</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>neighbourhood</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -6609,49 +6749,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in</t>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Book / some walk-in</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>11–17</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>08–18</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>08–18</t>
+          <t>17–23 kitchen 21:30</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>08–18</t>
+          <t>17–23 kitchen 21:30</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t>08–18 morning</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>1957 family café; giant cinnamon bun. Near ADM.</t>
+          <t>Kallio-scale BasBas cousin. Closed Sun–Mon.</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>Korvapuusti</t>
+          <t>Small plates</t>
         </is>
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>https://succes.fi/en/frontpage/</t>
+          <t>https://www.thealleyhelsinki.com/</t>
         </is>
       </c>
       <c r="P29" s="8" t="inlineStr">
@@ -6666,22 +6806,22 @@
     <row r="30" ht="52" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Eromanga</t>
+          <t>Way Bakery Kallio</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Bakery / lihapiirakka</t>
+          <t>Bakery / wine</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Kaartinkaupunki</t>
+          <t>Kallio</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Pohjoinen Makasiinikatu 6</t>
+          <t>Agricolankatu 9</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -6696,47 +6836,47 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Walk-in</t>
+          <t>No reservations</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>09–16</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>07:30–15:30</t>
+          <t>08–19</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>07:30–15:30</t>
+          <t>08–19</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>07:30–15:30</t>
+          <t>08–19</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>07:30–15:30 if buffer</t>
+          <t>08–19 morning</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>1946-recipe meat pie. Savoury bakery, not another bun.</t>
+          <t>Sourdough that can hold a Kallio morning. Not a Fazer clone.</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>Lihapiirakka</t>
+          <t>Bread + coffee; wine later</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>https://eromanga.fi/home/</t>
+          <t>https://www.waybakery.fi/kallio</t>
         </is>
       </c>
       <c r="P30" s="8" t="inlineStr">
@@ -6745,28 +6885,28 @@
         </is>
       </c>
       <c r="Q30" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" ht="52" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Kannas</t>
+          <t>Café Succès</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Finnish port classic</t>
+          <t>Traditional café</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Hietalahti</t>
+          <t>Ullanlinna</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Eerikinkatu 43</t>
+          <t>Korkeavuorenkatu 2</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -6779,49 +6919,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>Book dinner</t>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>14–24 kitchen 22:30</t>
+          <t>11–17</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>16–24 kitchen 22:30</t>
+          <t>08–18</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>08–18</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>08–18</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>too late</t>
+          <t>08–18 morning</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>Since 1939; sailors/dockworkers room. Less polished than Sea Horse.</t>
+          <t>1957 family café; giant cinnamon bun. Near ADM.</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>Finnish classics</t>
+          <t>Korvapuusti</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>https://kannas.fi/english/</t>
+          <t>https://succes.fi/en/frontpage/</t>
         </is>
       </c>
       <c r="P31" s="8" t="inlineStr">
@@ -6836,22 +6976,22 @@
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Cella</t>
+          <t>Eromanga</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Finnish neighbourhood classic</t>
+          <t>Bakery / lihapiirakka</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Kallio</t>
+          <t>Kaartinkaupunki</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Fleminginkatu 15</t>
+          <t>Pohjoinen Makasiinikatu 6</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -6866,77 +7006,77 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Call / walk-in</t>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>15–22</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>15–23</t>
+          <t>07:30–15:30</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>hours not yet published*</t>
+          <t>07:30–15:30</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>hours not yet published*</t>
+          <t>07:30–15:30</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>too late</t>
+          <t>07:30–15:30 if buffer</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>Since 1969; non-grand Kallio classic. Official page only lists through Mon 17 Aug — VERIFY Tue–Thu.</t>
+          <t>1946-recipe meat pie. Savoury bakery, not another bun.</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>Finnish pub-restaurant</t>
+          <t>Lihapiirakka</t>
         </is>
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>https://www.ravintolacella.fi/</t>
+          <t>https://eromanga.fi/home/</t>
         </is>
       </c>
       <c r="P32" s="8" t="inlineStr">
         <is>
-          <t>Official through 17 Aug</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="Q32" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" ht="52" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Carelia</t>
+          <t>Kannas</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>French brasserie</t>
+          <t>Finnish port classic</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Taka-Töölö</t>
+          <t>Hietalahti</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Mannerheimintie 56</t>
+          <t>Eerikinkatu 43</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -6951,27 +7091,27 @@
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Book dinner</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>14–24 kitchen 22:30</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>16–24 kitchen 22:30</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>16–23</t>
+          <t>same</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>16–23</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -6981,17 +7121,17 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>1920s pharmacy room. Summer break ended 12 Aug 2026. Closed Sun–Mon.</t>
+          <t>Since 1939; sailors/dockworkers room. Less polished than Sea Horse.</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Brasserie, not a Finnish-national menu</t>
+          <t>Finnish classics</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>https://ravintolacarelia.fi/en/home-2/</t>
+          <t>https://kannas.fi/english/</t>
         </is>
       </c>
       <c r="P33" s="8" t="inlineStr">
@@ -7006,12 +7146,12 @@
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Harju 8</t>
+          <t>Cella</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Bistro / natural wine</t>
+          <t>Finnish neighbourhood classic</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -7021,7 +7161,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Harjutori 8</t>
+          <t>Fleminginkatu 15</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -7036,27 +7176,27 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Walk-in — no reservation</t>
+          <t>Call / walk-in</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>11–late*</t>
+          <t>15–22</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>11–late*</t>
+          <t>15–23</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>11–late*</t>
+          <t>hours not yet published*</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>11–late*</t>
+          <t>hours not yet published*</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
@@ -7066,22 +7206,22 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>Spontaneous Kallio living room. Exact kitchen close not on MyHelsinki — VERIFY food service.</t>
+          <t>Since 1969; non-grand Kallio classic. Official page only lists through Mon 17 Aug — VERIFY Tue–Thu.</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Wine + plates; expect a wait</t>
+          <t>Finnish pub-restaurant</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>https://www.myhelsinki.fi/places/harju-8/</t>
+          <t>https://www.ravintolacella.fi/</t>
         </is>
       </c>
       <c r="P34" s="8" t="inlineStr">
         <is>
-          <t>MyHelsinki daily 11–late</t>
+          <t>Official through 17 Aug</t>
         </is>
       </c>
       <c r="Q34" s="8" t="n">
@@ -7091,27 +7231,27 @@
     <row r="35" ht="52" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Lohtu</t>
+          <t>Carelia</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Vegan hall lunch</t>
+          <t>French brasserie</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Hakaniemi Market Hall 2F</t>
+          <t>Taka-Töölö</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Hämeentie 1 A</t>
+          <t>Mannerheimintie 56</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>cheap-everyday</t>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -7119,49 +7259,49 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in lunch</t>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Book</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>CLOSED (hall)</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>lunch 11–15:30; porridge 08:30–10:30</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>16–23</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>16–23</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>lunch if buffer</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>Plant-based hall lunch. Not a dinner. Hall closed Sunday.</t>
+          <t>1920s pharmacy room. Summer break ended 12 Aug 2026. Closed Sun–Mon.</t>
         </is>
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>Vegan comfort lunch</t>
+          <t>Brasserie, not a Finnish-national menu</t>
         </is>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>https://www.ravintolalohtu.fi/en/</t>
+          <t>https://ravintolacarelia.fi/en/home-2/</t>
         </is>
       </c>
       <c r="P35" s="8" t="inlineStr">
@@ -7176,162 +7316,162 @@
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Sea Horse</t>
+          <t>Harju 8</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Classic Finnish</t>
+          <t>Bistro / natural wine</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Ullanlinna</t>
+          <t>Kallio</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Kapteeninkatu 11</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>icon</t>
+          <t>Harjutori 8</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>Book / walk-in</t>
+          <t>VERIFY lunch prices</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in — no reservation</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>15–24</t>
+          <t>11–late; kitchen 11–22</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>15–24</t>
+          <t>same; weekday lunch 11–15</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>15–24</t>
+          <t>same</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>15–24</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>15–24 (too late to start)</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>1933 institution; onion steak; near ADM</t>
+          <t>Spontaneous Kallio living room. Official: no reservations.</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>Onion steak / Baltic herring / vorschmack</t>
+          <t>Wine + plates; expect a wait</t>
         </is>
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>https://www.seahorse.fi/en/restaurant-sea-horse/</t>
+          <t>https://harju8.fi/info/</t>
         </is>
       </c>
       <c r="P36" s="8" t="inlineStr">
         <is>
-          <t>Official summer 8.6.2026+</t>
+          <t>Official kitchen 11–22</t>
         </is>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" ht="52" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Kosmos</t>
+          <t>Lohtu</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Helsinki classic</t>
+          <t>Vegan hall lunch</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Kamppi</t>
+          <t>Hakaniemi Market Hall 2F</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Kalevankatu 3</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>icon</t>
+          <t>Hämeentie 1 A</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>cheap-everyday</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Menu printed; VERIFY</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Phone / email</t>
+          <t>Walk-in lunch</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>CLOSED (hall)</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>11:30–24</t>
+          <t>lunch 11–15:30; porridge 08:30–10:30</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>11:30–24</t>
+          <t>same</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>11:30–24</t>
+          <t>same</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>11:30–24</t>
+          <t>lunch if buffer</t>
         </is>
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>1924; blinis, vorschmack, Baltic herring. Closed Sundays.</t>
+          <t>Plant-based hall lunch. Not a dinner. Hall closed Sunday.</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>Fried Baltic herrings 22€ on fetched menu</t>
+          <t>Vegan comfort lunch</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>https://kosmos.fi/en/our-food/</t>
+          <t>https://www.ravintolalohtu.fi/en/</t>
         </is>
       </c>
       <c r="P37" s="8" t="inlineStr">
@@ -7340,28 +7480,28 @@
         </is>
       </c>
       <c r="Q37" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" ht="52" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Sea Horse</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Artist restaurant</t>
+          <t>Classic Finnish</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Töölö</t>
+          <t>Ullanlinna</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Eteläinen Hesperiankatu 22</t>
+          <t>Kapteeninkatu 11</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -7376,167 +7516,167 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Book / walk-in</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>13–22</t>
+          <t>15–24</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>12–22</t>
+          <t>15–24</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>12–22</t>
+          <t>15–24</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>12–23</t>
+          <t>15–24</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>12–23</t>
+          <t>15–24 (too late to start)</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>Since 1932; onion steak cousin in Töölö</t>
+          <t>1933 institution; onion steak; near ADM</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>Classic Finnish</t>
+          <t>Onion steak / Baltic herring / vorschmack</t>
         </is>
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>https://elite.fi/en/front-page/</t>
+          <t>https://www.seahorse.fi/en/restaurant-sea-horse/</t>
         </is>
       </c>
       <c r="P38" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official summer 8.6.2026+</t>
         </is>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" ht="52" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Yes Yes Yes</t>
+          <t>Kosmos</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Vegetarian seasonal</t>
+          <t>Helsinki classic</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Punavuori</t>
+          <t>Kamppi</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Iso Roobertinkatu 1</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>hot</t>
+          <t>Kalevankatu 3</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>Menu printed; VERIFY</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>Walk-in / book</t>
+          <t>Phone / email</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11:30–24</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11:30–24</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11:30–24</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>11:30–24</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>Local-farm veg; wine. Hours not on official info page.</t>
+          <t>1924; blinis, vorschmack, Baltic herring. Closed Sundays.</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>Seasonal plates</t>
+          <t>Fried Baltic herrings 22€ on fetched menu</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>https://yesyesyes.fi/</t>
+          <t>https://kosmos.fi/en/our-food/</t>
         </is>
       </c>
       <c r="P39" s="8" t="inlineStr">
         <is>
-          <t>Official address; hours VERIFY</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" ht="52" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Löyly Restaurant</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Finnish casual / terrace</t>
+          <t>Artist restaurant</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Hernesaari</t>
+          <t>Töölö</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Hernesaarenranta 4</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>neighbourhood</t>
+          <t>Eteläinen Hesperiankatu 22</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -7544,54 +7684,54 @@
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>Walk-in terrace</t>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Book</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Kitchen 11–22</t>
+          <t>13–22</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>Kitchen 11–23</t>
+          <t>12–22</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>Kitchen 11–23</t>
+          <t>12–22</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>Kitchen 11–23</t>
+          <t>12–23</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>Kitchen 11–23</t>
+          <t>12–23</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>After sauna — not a destination kitchen</t>
+          <t>Since 1932; onion steak cousin in Töölö</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>Lohikeitto</t>
+          <t>Classic Finnish</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>https://www.loylyhelsinki.fi/en/info</t>
+          <t>https://elite.fi/en/front-page/</t>
         </is>
       </c>
       <c r="P40" s="8" t="inlineStr">
         <is>
-          <t>Official kitchen hours</t>
+          <t>Official</t>
         </is>
       </c>
       <c r="Q40" s="8" t="n">
@@ -7601,527 +7741,527 @@
     <row r="41" ht="52" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Finnjävel Salonki</t>
+          <t>Yes Yes Yes</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Finnish fine dining</t>
+          <t>Vegetarian seasonal</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Kamppi</t>
+          <t>Punavuori</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Ainonkatu 3</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>icon</t>
+          <t>Iso Roobertinkatu 1</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>hot</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>star-tier VERIFY</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>Book</t>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in / book</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>17–23</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>17–23</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>Leave 15:00</t>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>Michelin; skip unless you decide to blow the budget. Summer holiday already over.</t>
+          <t>Local-farm veg; wine. Hours not on official info page.</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Tasting</t>
+          <t>Seasonal plates</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>https://finnjavel.fi/en/</t>
+          <t>https://yesyesyes.fi/</t>
         </is>
       </c>
       <c r="P41" s="8" t="inlineStr">
         <is>
-          <t>Official hours</t>
+          <t>Official address; hours VERIFY</t>
         </is>
       </c>
       <c r="Q41" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" ht="52" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Olo / Palace</t>
+          <t>Löyly Restaurant</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Nordic 1–2★</t>
+          <t>Finnish casual / terrace</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Harbour</t>
+          <t>Hernesaari</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>VERIFY live</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>icon</t>
+          <t>Hernesaarenranta 4</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>neighbourhood</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>200+ VERIFY</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>Book weeks ahead</t>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>Walk-in terrace</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>Kitchen 11–22</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>Kitchen 11–23</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>Kitchen 11–23</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>Kitchen 11–23</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>Leave 15:00</t>
+          <t>Kitchen 11–23</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>Blow-budget. Skip unless you choose to.</t>
+          <t>After sauna — not a destination kitchen</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Tasting</t>
-        </is>
-      </c>
-      <c r="O42" s="8" t="inlineStr">
-        <is>
-          <t>Michelin / official sites</t>
+          <t>Lohikeitto</t>
+        </is>
+      </c>
+      <c r="O42" s="11" t="inlineStr">
+        <is>
+          <t>https://www.loylyhelsinki.fi/en/info</t>
         </is>
       </c>
       <c r="P42" s="8" t="inlineStr">
         <is>
-          <t>Not fetched in full this pass</t>
+          <t>Official kitchen hours</t>
         </is>
       </c>
       <c r="Q42" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" ht="52" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
+          <t>Finnjävel Salonki</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Finnish fine dining</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Töölönlahti</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Ainonkatu 3</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Salonki 108e / 138e official</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>17–23</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>17–23</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>Leave 15:00</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>Skip unless you decide to. Sali lunch exists Tue–Fri 11:30–15:00 — Thursday lunch collides with 15:00 out.</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t>Tasting</t>
+        </is>
+      </c>
+      <c r="O43" s="11" t="inlineStr">
+        <is>
+          <t>https://finnjavel.fi/en/</t>
+        </is>
+      </c>
+      <c r="P43" s="8" t="inlineStr">
+        <is>
+          <t>Official hours + menus</t>
+        </is>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" ht="52" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Olo</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Nordic 1★</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Kruununhaka</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Pohjoisesplanadi 5</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Menu Olo 189e; Selected 109e official</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>Book DinnerBooking</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>18–24</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>18–24</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>Blow-budget alternative to Nolla on Tuesday. Polished harbour room, not the locked plan.</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t>Selected 109e if you must</t>
+        </is>
+      </c>
+      <c r="O44" s="11" t="inlineStr">
+        <is>
+          <t>https://olo-ravintola.fi/en/menu-olo/</t>
+        </is>
+      </c>
+      <c r="P44" s="8" t="inlineStr">
+        <is>
+          <t>Official hours + menu</t>
+        </is>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" ht="52" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Palace</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Nordic 2★</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>South Harbour</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Eteläranta 10, 10th floor</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>250e inc water/coffee official</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>Book DinnerBooking</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>dinner (clock VERIFY)</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>Biggest splurge. Wednesday only in this window. Skip unless you choose the landmark room.</t>
+        </is>
+      </c>
+      <c r="N45" s="8" t="inlineStr">
+        <is>
+          <t>Tasting; wine pairing 220e official</t>
+        </is>
+      </c>
+      <c r="O45" s="11" t="inlineStr">
+        <is>
+          <t>https://palacerestaurant.fi/en/menu</t>
+        </is>
+      </c>
+      <c r="P45" s="8" t="inlineStr">
+        <is>
+          <t>Official service days + menu</t>
+        </is>
+      </c>
+      <c r="Q45" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" ht="52" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
           <t>Nepalese (Kallio)</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Nepalese</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Kallio</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Pick a busy room</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>cheap-everyday</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>VERIFY</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>Walk-in</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>Many open</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Many open</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Many open</t>
         </is>
       </c>
-      <c r="K43" s="8" t="inlineStr">
+      <c r="K46" s="8" t="inlineStr">
         <is>
           <t>Many open</t>
         </is>
       </c>
-      <c r="L43" s="8" t="inlineStr">
+      <c r="L46" s="8" t="inlineStr">
         <is>
           <t>Light only</t>
         </is>
       </c>
-      <c r="M43" s="8" t="inlineStr">
+      <c r="M46" s="8" t="inlineStr">
         <is>
           <t>Helsinki's kebabpizza analogue — ordinary diaspora lunch</t>
         </is>
       </c>
-      <c r="N43" s="8" t="inlineStr">
+      <c r="N46" s="8" t="inlineStr">
         <is>
           <t>Dal bhat / momo</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O46" s="8" t="inlineStr">
         <is>
           <t>Walk Hämeentie</t>
         </is>
       </c>
-      <c r="P43" s="8" t="inlineStr">
+      <c r="P46" s="8" t="inlineStr">
         <is>
           <t>Neighbourhood observation, not a single venue</t>
         </is>
       </c>
-      <c r="Q43" s="8" t="n">
+      <c r="Q46" s="8" t="n">
         <v>6</v>
-      </c>
-    </row>
-    <row r="44" ht="52" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>Savotta / Zetor / Kappeli</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>Tourist Finnish</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>Senate Square / Esplanadi</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>skip</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="12" t="inlineStr">
-        <is>
-          <t>Postcard Finland</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="inlineStr">
-        <is>
-          <t>Don't</t>
-        </is>
-      </c>
-      <c r="O44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P44" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q44" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="52" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>Sushi buffet chains</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>Buffet</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>Everywhere</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>skip</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M45" s="12" t="inlineStr">
-        <is>
-          <t>Not Domo</t>
-        </is>
-      </c>
-      <c r="N45" s="12" t="inlineStr">
-        <is>
-          <t>Don't</t>
-        </is>
-      </c>
-      <c r="O45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q45" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="52" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>Momotoko</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>Ramen CLOSED</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>Yliopistonkatu 5 (former)</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>skip</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>DEAD</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>DEAD</t>
-        </is>
-      </c>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>DEAD</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>DEAD</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>DEAD</t>
-        </is>
-      </c>
-      <c r="M46" s="12" t="inlineStr">
-        <is>
-          <t>Cathywong Oy bankruptcy May 2025; chain said permanently closed</t>
-        </is>
-      </c>
-      <c r="N46" s="12" t="inlineStr">
-        <is>
-          <t>Do not go</t>
-        </is>
-      </c>
-      <c r="O46" s="14" t="inlineStr">
-        <is>
-          <t>https://www.hs.fi/helsinki/art-2000011230551.html</t>
-        </is>
-      </c>
-      <c r="P46" s="12" t="inlineStr">
-        <is>
-          <t>HS 15.5.2025 + MTV 31.5.2025</t>
-        </is>
-      </c>
-      <c r="Q46" s="12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="47" ht="52" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Wino</t>
+          <t>Savotta / Zetor / Kappeli</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Wine bar CLOSED this trip</t>
+          <t>Tourist Finnish</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Fleminginkatu 11</t>
+          <t>Senate Square / Esplanadi</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -8146,32 +8286,32 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>CLOSED 1.6–3.9.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
-          <t>Facade renovation. Do not go.</t>
+          <t>Postcard Finland</t>
         </is>
       </c>
       <c r="N47" s="12" t="inlineStr">
@@ -8179,14 +8319,14 @@
           <t>Don't</t>
         </is>
       </c>
-      <c r="O47" s="14" t="inlineStr">
-        <is>
-          <t>https://www.wino.fi/restaurant-wino/</t>
+      <c r="O47" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>Official closure notice</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q47" s="12" t="n">
@@ -8196,17 +8336,17 @@
     <row r="48" ht="52" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Restaurant Kuu</t>
+          <t>Sushi buffet chains</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Töölö classic CLOSED</t>
+          <t>Buffet</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Töölönkatu 27</t>
+          <t>Everywhere</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -8231,32 +8371,32 @@
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>CLOSED from 1.7.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>same</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
-          <t>Housing-company renovation; reopen autumn. Don't google-walk there.</t>
+          <t>Not Domo</t>
         </is>
       </c>
       <c r="N48" s="12" t="inlineStr">
@@ -8264,14 +8404,14 @@
           <t>Don't</t>
         </is>
       </c>
-      <c r="O48" s="14" t="inlineStr">
-        <is>
-          <t>https://ravintolakuu.fi/en/kuu-closed-from-1-7/</t>
+      <c r="O48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q48" s="12" t="n">
@@ -8281,17 +8421,17 @@
     <row r="49" ht="52" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Adzika / Satkar / Sandro</t>
+          <t>Momotoko</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Moved or dead names</t>
+          <t>Ramen CLOSED</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>stale maps</t>
+          <t>Yliopistonkatu 5 (former)</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -8316,55 +8456,310 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>TRAP</t>
+          <t>DEAD</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>TRAP</t>
+          <t>DEAD</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>TRAP</t>
+          <t>DEAD</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>TRAP</t>
+          <t>DEAD</t>
         </is>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>TRAP</t>
+          <t>DEAD</t>
         </is>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
-          <t>Adzika seeking premises; Satkar is now Sansar; Sandro closed 28 Feb.</t>
+          <t>Cathywong Oy bankruptcy May 2025; chain said permanently closed</t>
         </is>
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
-          <t>Search current names</t>
-        </is>
-      </c>
-      <c r="O49" s="12" t="inlineStr">
-        <is>
-          <t>See research/neighbourhood-eateries.md</t>
+          <t>Do not go</t>
+        </is>
+      </c>
+      <c r="O49" s="14" t="inlineStr">
+        <is>
+          <t>https://www.hs.fi/helsinki/art-2000011230551.html</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>Official closure pages</t>
+          <t>HS 15.5.2025 + MTV 31.5.2025</t>
         </is>
       </c>
       <c r="Q49" s="12" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="50" ht="52" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Wino</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Wine bar CLOSED this trip</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>Fleminginkatu 11</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>CLOSED 1.6–3.9.2026</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="M50" s="12" t="inlineStr">
+        <is>
+          <t>Facade renovation. Do not go.</t>
+        </is>
+      </c>
+      <c r="N50" s="12" t="inlineStr">
+        <is>
+          <t>Don't</t>
+        </is>
+      </c>
+      <c r="O50" s="14" t="inlineStr">
+        <is>
+          <t>https://www.wino.fi/restaurant-wino/</t>
+        </is>
+      </c>
+      <c r="P50" s="12" t="inlineStr">
+        <is>
+          <t>Official closure notice</t>
+        </is>
+      </c>
+      <c r="Q50" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="52" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Restaurant Kuu</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Töölö classic CLOSED</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>Töölönkatu 27</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>CLOSED from 1.7.2026</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="K51" s="12" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+      <c r="M51" s="12" t="inlineStr">
+        <is>
+          <t>Housing-company renovation; reopen autumn. Don't google-walk there.</t>
+        </is>
+      </c>
+      <c r="N51" s="12" t="inlineStr">
+        <is>
+          <t>Don't</t>
+        </is>
+      </c>
+      <c r="O51" s="14" t="inlineStr">
+        <is>
+          <t>https://ravintolakuu.fi/en/kuu-closed-from-1-7/</t>
+        </is>
+      </c>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="Q51" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="52" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Adzika / Satkar / Sandro</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Moved or dead names</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>stale maps</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>TRAP</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>TRAP</t>
+        </is>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>TRAP</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>TRAP</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr">
+        <is>
+          <t>TRAP</t>
+        </is>
+      </c>
+      <c r="M52" s="12" t="inlineStr">
+        <is>
+          <t>Adzika seeking premises; Satkar is now Sansar; Sandro closed 28 Feb.</t>
+        </is>
+      </c>
+      <c r="N52" s="12" t="inlineStr">
+        <is>
+          <t>Search current names</t>
+        </is>
+      </c>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t>See research/neighbourhood-eateries.md</t>
+        </is>
+      </c>
+      <c r="P52" s="12" t="inlineStr">
+        <is>
+          <t>Official closure pages</t>
+        </is>
+      </c>
+      <c r="Q52" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q49"/>
+  <autoFilter ref="A1:Q52"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId2"/>
@@ -8381,32 +8776,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9763,7 +10163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10148,27 +10548,27 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Skörd</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>CLOSED*</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>OPEN dinner*</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>OPEN dinner*</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>OPEN dinner*</t>
+          <t>Shii</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -10178,34 +10578,34 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Official 86e/72e; hours Time Out Mon–Sat</t>
+          <t>Official omits weekly hours</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Kuurna</t>
+          <t>Hanayagi</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 17–23</t>
+          <t>CLOSED*</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED*</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>OPEN 17–23</t>
+          <t>OPEN 18–20:30*</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>OPEN 17–23</t>
+          <t>OPEN 18–20:30*</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -10215,209 +10615,209 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>TableOnline — VERIFY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Sea Horse</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 15–24</t>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>OPEN 15–24</t>
+          <t>OPEN 11–14:30 &amp; 17–21</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>OPEN 15–24</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>OPEN 15–24</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>OPEN but leaving</t>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>lunch if buffer</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Official summer</t>
+          <t>Official</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Kosmos</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
+          <t>Lia</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 15–22</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED?*</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 11:30–24</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>OPEN morning/lunch</t>
+          <t>OPEN 16–22</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official pages conflict on Monday</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 13–22</t>
+          <t>Skörd</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED*</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>OPEN 12–22</t>
+          <t>OPEN dinner*</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN dinner*</t>
         </is>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>OPEN morning</t>
+          <t>OPEN dinner*</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official 86e/72e; hours Time Out Mon–Sat</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Katana Ramen</t>
+          <t>Kuurna</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>CLOSED?*</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–21*</t>
+          <t>OPEN 17–23</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>OPEN*</t>
+          <t>OPEN 17–23</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>OPEN*</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>OPEN* morning</t>
+          <t>OPEN 17–23</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Falstaff — VERIFY</t>
+          <t>Official</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Bui Ramen</t>
+          <t>Sea Horse</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>OPEN 12–20</t>
+          <t>OPEN 15–24</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–21</t>
+          <t>OPEN 15–24</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN 15–24</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN 15–24</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>OPEN morning</t>
+          <t>OPEN but leaving</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Official — not central</t>
+          <t>Official summer</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Sansar</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 12–21</t>
+          <t>Kosmos</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>OPEN 10:30–21</t>
+          <t>OPEN 11:30–24</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
@@ -10430,46 +10830,46 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>lunch if time</t>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>OPEN morning/lunch</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Official — search Sansar not Satkar</t>
+          <t>Official</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>BasBas</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 13–22</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 12–22</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>OPEN from 16:00</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>OPEN from 16:00</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>too late</t>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>OPEN morning</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -10481,375 +10881,523 @@
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Cella</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 15–22</t>
+          <t>Katana Ramen</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED?*</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>OPEN 15–23</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>VERIFY</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>too late</t>
+          <t>OPEN 11–21*</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>OPEN*</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>OPEN*</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>OPEN* morning</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Official only through 17 Aug</t>
+          <t>Falstaff — VERIFY</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Carelia</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
+          <t>Bui Ramen</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 12–20</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–21</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>OPEN 16–23</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>OPEN 16–23</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>too late</t>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>OPEN morning</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Official; summer break ended 12 Aug</t>
+          <t>Official — not central</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Harju 8</t>
+          <t>Sansar</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–late*</t>
+          <t>OPEN 12–21</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>OPEN*</t>
+          <t>OPEN 10:30–21</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>OPEN*</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>OPEN*</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>too late</t>
+          <t>lunch if time</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>MyHelsinki — kitchen VERIFY</t>
+          <t>Official — search Sansar not Satkar</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Lohtu</t>
+          <t>BasBas</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>CLOSED (hall)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>OPEN lunch 11–15:30</t>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>OPEN lunch</t>
+          <t>OPEN from 16:00</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>OPEN lunch</t>
+          <t>OPEN from 16:00</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>lunch if buffer</t>
+          <t>too late</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Official; hall closed Sun</t>
+          <t>Official</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Amos Rex</t>
+          <t>Cella</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–17</t>
+          <t>OPEN 15–22</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–20</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 11–20</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 11–23 (you miss evening)</t>
+          <t>OPEN 15–23</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>VERIFY</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official only through 17 Aug</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>ADM</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 11–18</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 11–20</t>
+          <t>Carelia</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–20</t>
+          <t>OPEN 16–23</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–20</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 11–22 (you miss evening)</t>
+          <t>OPEN 16–23</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official; summer break ended 12 Aug</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Oodi</t>
+          <t>Harju 8</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>OPEN 10–20</t>
+          <t>OPEN 11–late*</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>OPEN 8–21</t>
+          <t>OPEN*</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>OPEN 8–21</t>
+          <t>OPEN*</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>OPEN 8–21</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 8–21 morning</t>
+          <t>OPEN*</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>too late</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>MyHelsinki — kitchen VERIFY</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Löyly sauna</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 11–21</t>
+          <t>Lohtu</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED (hall)</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>OPEN 12–22</t>
+          <t>OPEN lunch 11–15:30</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>OPEN 12–22</t>
+          <t>OPEN lunch</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>OPEN 9–11 &amp; 13–22</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 12–22 morning?</t>
+          <t>OPEN lunch</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>lunch if buffer</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Official</t>
+          <t>Official; hall closed Sun</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Ateneum</t>
+          <t>Amos Rex</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>OPEN 10–17</t>
+          <t>OPEN 11–17</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>OPEN 11–17</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>OPEN 10–18</t>
+          <t>OPEN 11–20</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>OPEN 10–20</t>
+          <t>OPEN 11–20</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>FREE 10–20</t>
+          <t>OPEN 11–23 (you miss evening)</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Official; free day 20 Aug</t>
+          <t>Official</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–18</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–20</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–20</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–20</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–22 (you miss evening)</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Oodi</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 10–20</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 8–21</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 8–21</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 8–21</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 8–21 morning</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Löyly sauna</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–21</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 12–22</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 12–22</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 9–11 &amp; 13–22</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 12–22 morning?</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Ateneum</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 10–17</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 11–17</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 10–18</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>OPEN 10–20</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>FREE 10–20</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Official; free day 20 Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
           <t>Momotoko</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
         <is>
           <t>DEAD</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>HS/MTV 2025</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G29"/>
+  <autoFilter ref="A1:G33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
